--- a/resource/result.xlsx
+++ b/resource/result.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b1fc4107772a6185/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_Files\_Lessons\ALGORITHM\Project\resource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="134" documentId="11_AD4DA82427541F7ACA7EB81580C8144E6BE8DE09" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F227C51C-383E-4919-94FE-5D99166021FA}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3807DC54-1680-4D77-A835-FEDEAF71506A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="bfs-0" sheetId="6" r:id="rId1"/>
@@ -20,6 +20,8 @@
     <sheet name="dp-0" sheetId="4" r:id="rId5"/>
     <sheet name="greedy" sheetId="7" r:id="rId6"/>
     <sheet name="MST" sheetId="8" r:id="rId7"/>
+    <sheet name="EXACT" sheetId="9" r:id="rId8"/>
+    <sheet name="APPRO" sheetId="10" r:id="rId9"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -31,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="21">
   <si>
     <t>name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -68,6 +70,50 @@
   </si>
   <si>
     <t>fri26</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dataset1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dataset2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MIN_COST</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Time</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dfs</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rec_cnt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>greedy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>min_cost</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ratio</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MST</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -111,10 +157,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -131,10 +183,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -804,4 +852,125 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FD5032F-7D46-42A8-94FF-8D70120A2E4C}">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.6640625" style="3"/>
+    <col min="2" max="2" width="12" style="3" customWidth="1"/>
+    <col min="3" max="16384" width="8.6640625" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="2"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B2" s="2"/>
+      <c r="C2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="B1:B2"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{260DB66E-1FFD-4D32-BA5D-DB6972467A37}">
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.6640625" style="3"/>
+    <col min="2" max="2" width="13.4140625" style="3" customWidth="1"/>
+    <col min="3" max="16384" width="8.6640625" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B2" s="2"/>
+      <c r="C2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="F1:H1"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/resource/result.xlsx
+++ b/resource/result.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_Files\_Lessons\ALGORITHM\Project\resource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C237B74-9C3D-4950-98C2-F27D505D39A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BFC3DE5-5D6D-421B-964B-B7DC593EE6E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXACT" sheetId="9" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="50">
   <si>
     <t>att48</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -223,6 +223,14 @@
   </si>
   <si>
     <t>ulyssses16</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DATASET</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Average Ratio</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -257,7 +265,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -265,23 +273,44 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -566,166 +595,184 @@
   <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" style="2"/>
-    <col min="2" max="2" width="12" style="2" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="8.6640625" style="2"/>
-    <col min="5" max="5" width="12.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.6640625" style="2"/>
-    <col min="7" max="7" width="12.75" style="2" customWidth="1"/>
-    <col min="8" max="8" width="8.6640625" style="2"/>
-    <col min="9" max="9" width="13.58203125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="11.4140625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="8.6640625" style="2"/>
-    <col min="12" max="12" width="10.9140625" style="2" customWidth="1"/>
-    <col min="13" max="16384" width="8.6640625" style="2"/>
+    <col min="1" max="1" width="8.6640625" style="1"/>
+    <col min="2" max="2" width="12" style="1" customWidth="1"/>
+    <col min="3" max="3" width="8.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="8.6640625" style="1"/>
+    <col min="5" max="5" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.6640625" style="1"/>
+    <col min="7" max="7" width="12.75" style="1" customWidth="1"/>
+    <col min="8" max="8" width="8.6640625" style="1"/>
+    <col min="9" max="9" width="13.58203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="11.4140625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="8.6640625" style="1"/>
+    <col min="12" max="12" width="10.9140625" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B1" s="4" t="s">
+      <c r="A1" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4" t="s">
+      <c r="E1" s="2"/>
+      <c r="F1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4" t="s">
+      <c r="G1" s="2"/>
+      <c r="H1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="4"/>
-      <c r="J1" s="2" t="s">
+      <c r="I1" s="2"/>
+      <c r="J1" s="3" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="4"/>
-      <c r="C2" s="2" t="s">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="3" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="6">
         <v>19</v>
       </c>
-      <c r="C3" s="2">
-        <v>0</v>
-      </c>
-      <c r="D3" s="1">
+      <c r="C3" s="3">
+        <v>0</v>
+      </c>
+      <c r="D3" s="6">
         <v>8467.33</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="6">
         <v>364724160</v>
       </c>
-      <c r="F3" s="1">
-        <v>0</v>
-      </c>
-      <c r="G3" s="1">
+      <c r="F3" s="6">
+        <v>0</v>
+      </c>
+      <c r="G3" s="6">
         <v>31</v>
       </c>
-      <c r="H3" s="1">
-        <v>0</v>
-      </c>
-      <c r="I3" s="1">
+      <c r="H3" s="6">
+        <v>0</v>
+      </c>
+      <c r="I3" s="6">
         <v>62</v>
       </c>
-      <c r="J3" s="1">
+      <c r="J3" s="6">
         <v>0.33</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="3">
         <v>291</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="3">
         <v>16</v>
       </c>
-      <c r="F4" s="1">
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="6">
         <v>34</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" s="6">
         <v>1613542</v>
       </c>
-      <c r="H4" s="1">
+      <c r="H4" s="6">
         <v>31786.33</v>
       </c>
-      <c r="I4" s="1">
+      <c r="I4" s="6">
         <v>207713158</v>
       </c>
+      <c r="J4" s="3"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="3">
         <v>71</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="3">
         <v>33</v>
       </c>
-      <c r="F5" s="2">
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3">
         <v>302456</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="3">
         <v>15887259562</v>
       </c>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="3">
         <v>2085</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="3">
         <v>70</v>
       </c>
-      <c r="F6" s="1">
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="6">
         <v>211214.33</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" s="6">
         <v>12457317253</v>
       </c>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="H1:I1"/>
+    <mergeCell ref="A1:A2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -734,923 +781,949 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{260DB66E-1FFD-4D32-BA5D-DB6972467A37}">
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" style="2"/>
-    <col min="2" max="2" width="13.4140625" style="2" customWidth="1"/>
-    <col min="3" max="16384" width="8.6640625" style="2"/>
+    <col min="1" max="1" width="11.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.4140625" style="1" customWidth="1"/>
+    <col min="3" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B1" s="4" t="s">
+      <c r="A1" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4" t="s">
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B2" s="4"/>
-      <c r="C2" s="2" t="s">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="3">
         <v>2579</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="3">
         <v>31</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="3">
         <v>2975</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="4">
         <f>D3/B3</f>
         <v>1.1535478867778208</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="3">
         <v>4514</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="3">
         <v>3313</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3" s="4">
         <f>G3/B3</f>
         <v>1.2846064366033347</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="2">
+      <c r="A4" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="3">
         <v>33523</v>
       </c>
-      <c r="C4" s="2">
-        <v>0</v>
-      </c>
-      <c r="D4" s="2">
+      <c r="C4" s="3">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3">
         <v>37928</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="4">
         <f t="shared" ref="E4:E33" si="0">D4/B4</f>
         <v>1.1314023207946782</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="3">
         <v>6</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="3">
         <v>41190</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="4">
         <f t="shared" ref="H4:H33" si="1">G4/B4</f>
         <v>1.2287086477940519</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="3">
         <v>9073</v>
       </c>
-      <c r="C5" s="2">
-        <v>0</v>
-      </c>
-      <c r="D5" s="2">
+      <c r="C5" s="3">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3">
         <v>9962</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="4">
         <f t="shared" si="0"/>
         <v>1.0979830265623278</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="3">
         <v>2</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="3">
         <v>10341</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="4">
         <f t="shared" si="1"/>
         <v>1.1397553179764135</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="3">
         <v>9290</v>
       </c>
-      <c r="C6" s="2">
-        <v>0</v>
-      </c>
-      <c r="D6" s="2">
+      <c r="C6" s="3">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3">
         <v>9962</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="4">
         <f t="shared" si="0"/>
         <v>1.0723358449946179</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="3">
         <v>1</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="3">
         <v>10341</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6" s="4">
         <f t="shared" si="1"/>
         <v>1.1131324004305705</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="3">
         <v>7542</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="3">
         <v>1</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="3">
         <v>8181</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="4">
         <f t="shared" si="0"/>
         <v>1.0847255369928401</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="3">
         <v>8</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7" s="3">
         <v>9550</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H7" s="4">
         <f t="shared" si="1"/>
         <v>1.2662423760275789</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="3">
         <v>6105</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="3">
         <v>5</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="3">
         <v>7049</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="4">
         <f t="shared" si="0"/>
         <v>1.1546273546273547</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="3">
         <v>234</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G8" s="3">
         <v>7906</v>
       </c>
-      <c r="H8" s="3">
+      <c r="H8" s="4">
         <f t="shared" si="1"/>
         <v>1.2950040950040951</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="3">
         <v>6527</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="3">
         <v>9</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="3">
         <v>7213</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="4">
         <f t="shared" si="0"/>
         <v>1.105101884479853</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="3">
         <v>416</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G9" s="3">
         <v>8140</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9" s="4">
         <f t="shared" si="1"/>
         <v>1.24712731729738</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="3">
         <v>629</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="3">
         <v>4</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="3">
         <v>746</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="4">
         <f t="shared" si="0"/>
         <v>1.1860095389507155</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="3">
         <v>85</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10" s="3">
         <v>822</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H10" s="4">
         <f t="shared" si="1"/>
         <v>1.3068362480127187</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="3">
         <v>426</v>
       </c>
-      <c r="C11" s="2">
-        <v>0</v>
-      </c>
-      <c r="D11" s="2">
+      <c r="C11" s="3">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3">
         <v>482</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="4">
         <f t="shared" si="0"/>
         <v>1.1314553990610328</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="3">
         <v>7</v>
       </c>
-      <c r="G11" s="2">
+      <c r="G11" s="3">
         <v>556</v>
       </c>
-      <c r="H11" s="3">
+      <c r="H11" s="4">
         <f t="shared" si="1"/>
         <v>1.3051643192488263</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="3">
         <v>538</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="3">
         <v>1</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="3">
         <v>608</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="4">
         <f t="shared" si="0"/>
         <v>1.1301115241635689</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="3">
         <v>29</v>
       </c>
-      <c r="G12" s="2">
+      <c r="G12" s="3">
         <v>674</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="4">
         <f t="shared" si="1"/>
         <v>1.2527881040892193</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="3">
         <v>19</v>
       </c>
-      <c r="C13" s="2">
-        <v>0</v>
-      </c>
-      <c r="D13" s="2">
+      <c r="C13" s="3">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3">
         <v>21</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="4">
         <f t="shared" si="0"/>
         <v>1.1052631578947369</v>
       </c>
-      <c r="F13" s="2">
-        <v>0</v>
-      </c>
-      <c r="G13" s="2">
+      <c r="F13" s="3">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3">
         <v>21</v>
       </c>
-      <c r="H13" s="3">
+      <c r="H13" s="4">
         <f t="shared" si="1"/>
         <v>1.1052631578947369</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="3">
         <v>937</v>
       </c>
-      <c r="C14" s="2">
-        <v>0</v>
-      </c>
-      <c r="D14" s="2">
+      <c r="C14" s="3">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3">
         <v>965</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="4">
         <f t="shared" si="0"/>
         <v>1.0298826040554963</v>
       </c>
-      <c r="F14" s="2">
-        <v>0</v>
-      </c>
-      <c r="G14" s="2">
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>1102</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="4">
         <f t="shared" si="1"/>
         <v>1.176093916755603</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="3">
         <v>1667</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="3">
         <v>4</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="3">
         <v>1836</v>
       </c>
-      <c r="E15" s="3">
+      <c r="E15" s="4">
         <f t="shared" si="0"/>
         <v>1.101379724055189</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="3">
         <v>169</v>
       </c>
-      <c r="G15" s="2">
+      <c r="G15" s="3">
         <v>2101</v>
       </c>
-      <c r="H15" s="3">
+      <c r="H15" s="4">
         <f t="shared" si="1"/>
         <v>1.2603479304139171</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="3">
         <v>2085</v>
       </c>
-      <c r="C16" s="2">
-        <v>0</v>
-      </c>
-      <c r="D16" s="2">
+      <c r="C16" s="3">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3">
         <v>2178</v>
       </c>
-      <c r="E16" s="3">
+      <c r="E16" s="4">
         <f t="shared" si="0"/>
         <v>1.0446043165467627</v>
       </c>
-      <c r="F16" s="2">
-        <v>0</v>
-      </c>
-      <c r="G16" s="2">
+      <c r="F16" s="3">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3">
         <v>2210</v>
       </c>
-      <c r="H16" s="3">
+      <c r="H16" s="4">
         <f t="shared" si="1"/>
         <v>1.0599520383693046</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="3">
         <v>533</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="3">
         <v>13</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="3">
         <v>547</v>
       </c>
-      <c r="E17" s="3">
+      <c r="E17" s="4">
         <f t="shared" si="0"/>
         <v>1.026266416510319</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17" s="3">
         <v>1306</v>
       </c>
-      <c r="G17" s="2">
+      <c r="G17" s="3">
         <v>588</v>
       </c>
-      <c r="H17" s="3">
+      <c r="H17" s="4">
         <f t="shared" si="1"/>
         <v>1.1031894934333959</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18" s="3">
         <v>3894</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C18" s="3">
         <v>341</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D18" s="3">
         <v>3711</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E18" s="4">
         <f t="shared" si="0"/>
         <v>0.95300462249614792</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F18" s="3">
         <v>109900</v>
       </c>
-      <c r="G18" s="2">
+      <c r="G18" s="3">
         <v>3967</v>
       </c>
-      <c r="H18" s="3">
+      <c r="H18" s="4">
         <f t="shared" si="1"/>
         <v>1.0187467899332305</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B19" s="3">
         <v>502</v>
       </c>
-      <c r="C19" s="2">
+      <c r="C19" s="3">
         <v>2</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D19" s="3">
         <v>583</v>
       </c>
-      <c r="E19" s="3">
+      <c r="E19" s="4">
         <f t="shared" si="0"/>
         <v>1.1613545816733069</v>
       </c>
-      <c r="F19" s="2">
+      <c r="F19" s="3">
         <v>69</v>
       </c>
-      <c r="G19" s="2">
+      <c r="G19" s="3">
         <v>634</v>
       </c>
-      <c r="H19" s="3">
+      <c r="H19" s="4">
         <f t="shared" si="1"/>
         <v>1.2629482071713147</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B20" s="2">
+      <c r="B20" s="3">
         <v>21282</v>
       </c>
-      <c r="C20" s="2">
+      <c r="C20" s="3">
         <v>2</v>
       </c>
-      <c r="D20" s="2">
+      <c r="D20" s="3">
         <v>24698</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" s="4">
         <f t="shared" si="0"/>
         <v>1.1605112301475424</v>
       </c>
-      <c r="F20" s="2">
+      <c r="F20" s="3">
         <v>84</v>
       </c>
-      <c r="G20" s="2">
+      <c r="G20" s="3">
         <v>26442</v>
       </c>
-      <c r="H20" s="3">
+      <c r="H20" s="4">
         <f t="shared" si="1"/>
         <v>1.2424584155624472</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B21" s="3">
         <v>20749</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C21" s="3">
         <v>3</v>
       </c>
-      <c r="D21" s="2">
+      <c r="D21" s="3">
         <v>23660</v>
       </c>
-      <c r="E21" s="3">
+      <c r="E21" s="4">
         <f t="shared" si="0"/>
         <v>1.1402959178755603</v>
       </c>
-      <c r="F21" s="2">
+      <c r="F21" s="3">
         <v>86</v>
       </c>
-      <c r="G21" s="2">
+      <c r="G21" s="3">
         <v>27130</v>
       </c>
-      <c r="H21" s="3">
+      <c r="H21" s="4">
         <f t="shared" si="1"/>
         <v>1.3075328931514771</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="2">
+      <c r="B22" s="3">
         <v>21294</v>
       </c>
-      <c r="C22" s="2">
+      <c r="C22" s="3">
         <v>3</v>
       </c>
-      <c r="D22" s="2">
+      <c r="D22" s="3">
         <v>24852</v>
       </c>
-      <c r="E22" s="3">
+      <c r="E22" s="4">
         <f t="shared" si="0"/>
         <v>1.1670893209354747</v>
       </c>
-      <c r="F22" s="2">
+      <c r="F22" s="3">
         <v>84</v>
       </c>
-      <c r="G22" s="2">
+      <c r="G22" s="3">
         <v>26002</v>
       </c>
-      <c r="H22" s="3">
+      <c r="H22" s="4">
         <f t="shared" si="1"/>
         <v>1.2210951441720672</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B23" s="2">
+      <c r="B23" s="3">
         <v>14379</v>
       </c>
-      <c r="C23" s="2">
+      <c r="C23" s="3">
         <v>3</v>
       </c>
-      <c r="D23" s="2">
+      <c r="D23" s="3">
         <v>16935</v>
       </c>
-      <c r="E23" s="3">
+      <c r="E23" s="4">
         <f t="shared" si="0"/>
         <v>1.177759232213645</v>
       </c>
-      <c r="F23" s="2">
+      <c r="F23" s="3">
         <v>100</v>
       </c>
-      <c r="G23" s="2">
+      <c r="G23" s="3">
         <v>18901</v>
       </c>
-      <c r="H23" s="3">
+      <c r="H23" s="4">
         <f t="shared" si="1"/>
         <v>1.3144864037832951</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B24" s="2">
+      <c r="B24" s="3">
         <v>291</v>
       </c>
-      <c r="C24" s="2">
-        <v>0</v>
-      </c>
-      <c r="D24" s="2">
+      <c r="C24" s="3">
+        <v>0</v>
+      </c>
+      <c r="D24" s="3">
         <v>291</v>
       </c>
-      <c r="E24" s="3">
+      <c r="E24" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F24" s="2">
-        <v>0</v>
-      </c>
-      <c r="G24" s="2">
+      <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
         <v>299</v>
       </c>
-      <c r="H24" s="3">
+      <c r="H24" s="4">
         <f t="shared" si="1"/>
         <v>1.0274914089347078</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B25" s="2">
+      <c r="B25" s="3">
         <v>19311</v>
       </c>
-      <c r="C25" s="2">
+      <c r="C25" s="3">
         <v>229</v>
       </c>
-      <c r="D25" s="2">
+      <c r="D25" s="3">
         <v>17927</v>
       </c>
-      <c r="E25" s="3">
+      <c r="E25" s="4">
         <f t="shared" si="0"/>
         <v>0.92833100305525351</v>
       </c>
-      <c r="F25" s="2">
+      <c r="F25" s="3">
         <v>70952</v>
       </c>
-      <c r="G25" s="2">
+      <c r="G25" s="3">
         <v>20958</v>
       </c>
-      <c r="H25" s="3">
+      <c r="H25" s="4">
         <f t="shared" si="1"/>
         <v>1.0852881777225416</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B26" s="2">
+      <c r="B26" s="3">
         <v>50778</v>
       </c>
-      <c r="C26" s="2">
+      <c r="C26" s="3">
         <v>132</v>
       </c>
-      <c r="D26" s="2">
+      <c r="D26" s="3">
         <v>58950</v>
       </c>
-      <c r="E26" s="3">
+      <c r="E26" s="4">
         <f t="shared" si="0"/>
         <v>1.1609358383551931</v>
       </c>
-      <c r="F26" s="2">
+      <c r="F26" s="3">
         <v>29490</v>
       </c>
-      <c r="G26" s="2">
+      <c r="G26" s="3">
         <v>68397</v>
       </c>
-      <c r="H26" s="3">
+      <c r="H26" s="4">
         <f t="shared" si="1"/>
         <v>1.3469809760132341</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B27" s="2">
+      <c r="B27" s="3">
         <v>259045</v>
       </c>
-      <c r="C27" s="2">
+      <c r="C27" s="3">
         <v>1196</v>
       </c>
-      <c r="D27" s="2">
+      <c r="D27" s="3">
         <v>313745</v>
       </c>
-      <c r="E27" s="3">
+      <c r="E27" s="4">
         <f t="shared" si="0"/>
         <v>1.2111602231272558</v>
       </c>
-      <c r="F27" s="2">
+      <c r="F27" s="3">
         <v>502354</v>
       </c>
-      <c r="G27" s="2">
+      <c r="G27" s="3">
         <v>347246</v>
       </c>
-      <c r="H27" s="3">
+      <c r="H27" s="4">
         <f t="shared" si="1"/>
         <v>1.3404852438765464</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B28" s="2">
+      <c r="B28" s="3">
         <v>108159</v>
       </c>
-      <c r="C28" s="2">
+      <c r="C28" s="3">
         <v>1</v>
       </c>
-      <c r="D28" s="2">
+      <c r="D28" s="3">
         <v>130921</v>
       </c>
-      <c r="E28" s="3">
+      <c r="E28" s="4">
         <f t="shared" si="0"/>
         <v>1.2104494309303895</v>
       </c>
-      <c r="F28" s="2">
+      <c r="F28" s="3">
         <v>29</v>
       </c>
-      <c r="G28" s="2">
+      <c r="G28" s="3">
         <v>142085</v>
       </c>
-      <c r="H28" s="3">
+      <c r="H28" s="4">
         <f t="shared" si="1"/>
         <v>1.3136678408639133</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B29" s="2">
+      <c r="B29" s="3">
         <v>7755</v>
       </c>
-      <c r="C29" s="2">
+      <c r="C29" s="3">
         <v>3</v>
       </c>
-      <c r="D29" s="2">
+      <c r="D29" s="3">
         <v>9424</v>
       </c>
-      <c r="E29" s="3">
+      <c r="E29" s="4">
         <f t="shared" si="0"/>
         <v>1.2152159896840748</v>
       </c>
-      <c r="F29" s="2">
+      <c r="F29" s="3">
         <v>84</v>
       </c>
-      <c r="G29" s="2">
+      <c r="G29" s="3">
         <v>10646</v>
       </c>
-      <c r="H29" s="3">
+      <c r="H29" s="4">
         <f t="shared" si="1"/>
         <v>1.3727917472598323</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B30" s="2">
+      <c r="B30" s="3">
         <v>675</v>
       </c>
-      <c r="C30" s="2">
+      <c r="C30" s="3">
         <v>1</v>
       </c>
-      <c r="D30" s="2">
+      <c r="D30" s="3">
         <v>796</v>
       </c>
-      <c r="E30" s="3">
+      <c r="E30" s="4">
         <f t="shared" si="0"/>
         <v>1.1792592592592592</v>
       </c>
-      <c r="F30" s="2">
+      <c r="F30" s="3">
         <v>22</v>
       </c>
-      <c r="G30" s="2">
+      <c r="G30" s="3">
         <v>862</v>
       </c>
-      <c r="H30" s="3">
+      <c r="H30" s="4">
         <f t="shared" si="1"/>
         <v>1.277037037037037</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B31" s="2">
+      <c r="B31" s="3">
         <v>3854</v>
       </c>
-      <c r="C31" s="2">
+      <c r="C31" s="3">
         <v>20</v>
       </c>
-      <c r="D31" s="2">
+      <c r="D31" s="3">
         <v>4647</v>
       </c>
-      <c r="E31" s="3">
+      <c r="E31" s="4">
         <f t="shared" si="0"/>
         <v>1.2057602490918526</v>
       </c>
-      <c r="F31" s="2">
+      <c r="F31" s="3">
         <v>1989</v>
       </c>
-      <c r="G31" s="2">
+      <c r="G31" s="3">
         <v>5122</v>
       </c>
-      <c r="H31" s="3">
+      <c r="H31" s="4">
         <f t="shared" si="1"/>
         <v>1.3290088220031135</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B32" s="2">
+      <c r="B32" s="3">
         <v>71</v>
       </c>
-      <c r="C32" s="2">
-        <v>0</v>
-      </c>
-      <c r="D32" s="2">
+      <c r="C32" s="3">
+        <v>0</v>
+      </c>
+      <c r="D32" s="3">
         <v>74</v>
       </c>
-      <c r="E32" s="3">
+      <c r="E32" s="4">
         <f t="shared" si="0"/>
         <v>1.0422535211267605</v>
       </c>
-      <c r="F32" s="2">
-        <v>0</v>
-      </c>
-      <c r="G32" s="2">
+      <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>72</v>
       </c>
-      <c r="H32" s="3">
+      <c r="H32" s="4">
         <f t="shared" si="1"/>
         <v>1.0140845070422535</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B33" s="2">
+      <c r="B33" s="3">
         <v>73</v>
       </c>
-      <c r="C33" s="2">
-        <v>0</v>
-      </c>
-      <c r="D33" s="2">
+      <c r="C33" s="3">
+        <v>0</v>
+      </c>
+      <c r="D33" s="3">
         <v>86</v>
       </c>
-      <c r="E33" s="3">
+      <c r="E33" s="4">
         <f t="shared" si="0"/>
         <v>1.178082191780822</v>
       </c>
-      <c r="F33" s="2">
+      <c r="F33" s="3">
         <v>2</v>
       </c>
-      <c r="G33" s="2">
+      <c r="G33" s="3">
         <v>75</v>
       </c>
-      <c r="H33" s="3">
+      <c r="H33" s="4">
         <f t="shared" si="1"/>
         <v>1.0273972602739727</v>
       </c>
     </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B34" s="2"/>
+      <c r="C34" s="5">
+        <f>AVERAGE(E3:E33)</f>
+        <v>1.11761803703935</v>
+      </c>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="5">
+        <f>AVERAGE(H3:H33)</f>
+        <v>1.2143778281984563</v>
+      </c>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="7">
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="F34:H34"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/resource/result.xlsx
+++ b/resource/result.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_Files\_Lessons\ALGORITHM\Project\resource\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b1fc4107772a6185/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BFC3DE5-5D6D-421B-964B-B7DC593EE6E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{5BFC3DE5-5D6D-421B-964B-B7DC593EE6E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6B9FAC1-3667-4000-84A6-A9AE6DB45EE1}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXACT" sheetId="9" r:id="rId1"/>
@@ -300,17 +300,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -611,160 +611,164 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2" t="s">
+      <c r="E1" s="5"/>
+      <c r="F1" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2" t="s">
+      <c r="G1" s="5"/>
+      <c r="H1" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="3" t="s">
+      <c r="I1" s="5"/>
+      <c r="J1" s="2" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="3" t="s">
+      <c r="A2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="2" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="4">
         <v>19</v>
       </c>
-      <c r="C3" s="3">
-        <v>0</v>
-      </c>
-      <c r="D3" s="6">
+      <c r="C3" s="2">
+        <v>0</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0</v>
+      </c>
+      <c r="E3" s="1">
+        <v>62</v>
+      </c>
+      <c r="F3" s="4">
+        <v>0</v>
+      </c>
+      <c r="G3" s="4">
+        <v>31</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0</v>
+      </c>
+      <c r="I3" s="4">
+        <v>62</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2">
+        <v>291</v>
+      </c>
+      <c r="C4" s="2">
+        <v>16</v>
+      </c>
+      <c r="D4" s="4">
         <v>8467.33</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E4" s="4">
         <v>364724160</v>
       </c>
-      <c r="F3" s="6">
-        <v>0</v>
-      </c>
-      <c r="G3" s="6">
-        <v>31</v>
-      </c>
-      <c r="H3" s="6">
-        <v>0</v>
-      </c>
-      <c r="I3" s="6">
-        <v>62</v>
-      </c>
-      <c r="J3" s="6">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="3">
-        <v>291</v>
-      </c>
-      <c r="C4" s="3">
-        <v>16</v>
-      </c>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="6">
+      <c r="F4" s="4">
         <v>34</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="4">
         <v>1613542</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="4">
         <v>31786.33</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="4">
         <v>207713158</v>
       </c>
-      <c r="J4" s="3"/>
+      <c r="J4" s="2"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="2">
         <v>71</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="2">
         <v>33</v>
       </c>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3">
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2">
         <v>302456</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="2">
         <v>15887259562</v>
       </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="2">
         <v>2085</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="2">
         <v>70</v>
       </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="6">
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="4">
         <v>211214.33</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="4">
         <v>12457317253</v>
       </c>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -790,930 +794,930 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2" t="s">
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="3" t="s">
+      <c r="A2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="2">
         <v>2579</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="2">
         <v>31</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="2">
         <v>2975</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="3">
         <f>D3/B3</f>
         <v>1.1535478867778208</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="2">
         <v>4514</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="2">
         <v>3313</v>
       </c>
-      <c r="H3" s="4">
+      <c r="H3" s="3">
         <f>G3/B3</f>
         <v>1.2846064366033347</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="3">
+      <c r="A4" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="2">
         <v>33523</v>
       </c>
-      <c r="C4" s="3">
-        <v>0</v>
-      </c>
-      <c r="D4" s="3">
+      <c r="C4" s="2">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2">
         <v>37928</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="3">
         <f t="shared" ref="E4:E33" si="0">D4/B4</f>
         <v>1.1314023207946782</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="2">
         <v>6</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="2">
         <v>41190</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4" s="3">
         <f t="shared" ref="H4:H33" si="1">G4/B4</f>
         <v>1.2287086477940519</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="2">
         <v>9073</v>
       </c>
-      <c r="C5" s="3">
-        <v>0</v>
-      </c>
-      <c r="D5" s="3">
+      <c r="C5" s="2">
+        <v>0</v>
+      </c>
+      <c r="D5" s="2">
         <v>9962</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="3">
         <f t="shared" si="0"/>
         <v>1.0979830265623278</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="2">
         <v>2</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="2">
         <v>10341</v>
       </c>
-      <c r="H5" s="4">
+      <c r="H5" s="3">
         <f t="shared" si="1"/>
         <v>1.1397553179764135</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="2">
         <v>9290</v>
       </c>
-      <c r="C6" s="3">
-        <v>0</v>
-      </c>
-      <c r="D6" s="3">
+      <c r="C6" s="2">
+        <v>0</v>
+      </c>
+      <c r="D6" s="2">
         <v>9962</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="3">
         <f t="shared" si="0"/>
         <v>1.0723358449946179</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="2">
         <v>1</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="2">
         <v>10341</v>
       </c>
-      <c r="H6" s="4">
+      <c r="H6" s="3">
         <f t="shared" si="1"/>
         <v>1.1131324004305705</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="2">
         <v>7542</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="2">
         <v>1</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="2">
         <v>8181</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="3">
         <f t="shared" si="0"/>
         <v>1.0847255369928401</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="2">
         <v>8</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7" s="2">
         <v>9550</v>
       </c>
-      <c r="H7" s="4">
+      <c r="H7" s="3">
         <f t="shared" si="1"/>
         <v>1.2662423760275789</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="2">
         <v>6105</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="2">
         <v>5</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="2">
         <v>7049</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="3">
         <f t="shared" si="0"/>
         <v>1.1546273546273547</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="2">
         <v>234</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8" s="2">
         <v>7906</v>
       </c>
-      <c r="H8" s="4">
+      <c r="H8" s="3">
         <f t="shared" si="1"/>
         <v>1.2950040950040951</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="2">
         <v>6527</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="2">
         <v>9</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="2">
         <v>7213</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="3">
         <f t="shared" si="0"/>
         <v>1.105101884479853</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="2">
         <v>416</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9" s="2">
         <v>8140</v>
       </c>
-      <c r="H9" s="4">
+      <c r="H9" s="3">
         <f t="shared" si="1"/>
         <v>1.24712731729738</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="2">
         <v>629</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="2">
         <v>4</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="2">
         <v>746</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="3">
         <f t="shared" si="0"/>
         <v>1.1860095389507155</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="2">
         <v>85</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10" s="2">
         <v>822</v>
       </c>
-      <c r="H10" s="4">
+      <c r="H10" s="3">
         <f t="shared" si="1"/>
         <v>1.3068362480127187</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="2">
         <v>426</v>
       </c>
-      <c r="C11" s="3">
-        <v>0</v>
-      </c>
-      <c r="D11" s="3">
+      <c r="C11" s="2">
+        <v>0</v>
+      </c>
+      <c r="D11" s="2">
         <v>482</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E11" s="3">
         <f t="shared" si="0"/>
         <v>1.1314553990610328</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="2">
         <v>7</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11" s="2">
         <v>556</v>
       </c>
-      <c r="H11" s="4">
+      <c r="H11" s="3">
         <f t="shared" si="1"/>
         <v>1.3051643192488263</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="2">
         <v>538</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="2">
         <v>1</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="2">
         <v>608</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="3">
         <f t="shared" si="0"/>
         <v>1.1301115241635689</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="2">
         <v>29</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="2">
         <v>674</v>
       </c>
-      <c r="H12" s="4">
+      <c r="H12" s="3">
         <f t="shared" si="1"/>
         <v>1.2527881040892193</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="2">
         <v>19</v>
       </c>
-      <c r="C13" s="3">
-        <v>0</v>
-      </c>
-      <c r="D13" s="3">
+      <c r="C13" s="2">
+        <v>0</v>
+      </c>
+      <c r="D13" s="2">
         <v>21</v>
       </c>
-      <c r="E13" s="4">
+      <c r="E13" s="3">
         <f t="shared" si="0"/>
         <v>1.1052631578947369</v>
       </c>
-      <c r="F13" s="3">
-        <v>0</v>
-      </c>
-      <c r="G13" s="3">
+      <c r="F13" s="2">
+        <v>0</v>
+      </c>
+      <c r="G13" s="2">
         <v>21</v>
       </c>
-      <c r="H13" s="4">
+      <c r="H13" s="3">
         <f t="shared" si="1"/>
         <v>1.1052631578947369</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="2">
         <v>937</v>
       </c>
-      <c r="C14" s="3">
-        <v>0</v>
-      </c>
-      <c r="D14" s="3">
+      <c r="C14" s="2">
+        <v>0</v>
+      </c>
+      <c r="D14" s="2">
         <v>965</v>
       </c>
-      <c r="E14" s="4">
+      <c r="E14" s="3">
         <f t="shared" si="0"/>
         <v>1.0298826040554963</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="F14" s="2">
+        <v>0</v>
+      </c>
+      <c r="G14" s="2">
         <v>1102</v>
       </c>
-      <c r="H14" s="4">
+      <c r="H14" s="3">
         <f t="shared" si="1"/>
         <v>1.176093916755603</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15" s="2">
         <v>1667</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="2">
         <v>4</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="2">
         <v>1836</v>
       </c>
-      <c r="E15" s="4">
+      <c r="E15" s="3">
         <f t="shared" si="0"/>
         <v>1.101379724055189</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="2">
         <v>169</v>
       </c>
-      <c r="G15" s="3">
+      <c r="G15" s="2">
         <v>2101</v>
       </c>
-      <c r="H15" s="4">
+      <c r="H15" s="3">
         <f t="shared" si="1"/>
         <v>1.2603479304139171</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16" s="2">
         <v>2085</v>
       </c>
-      <c r="C16" s="3">
-        <v>0</v>
-      </c>
-      <c r="D16" s="3">
+      <c r="C16" s="2">
+        <v>0</v>
+      </c>
+      <c r="D16" s="2">
         <v>2178</v>
       </c>
-      <c r="E16" s="4">
+      <c r="E16" s="3">
         <f t="shared" si="0"/>
         <v>1.0446043165467627</v>
       </c>
-      <c r="F16" s="3">
-        <v>0</v>
-      </c>
-      <c r="G16" s="3">
+      <c r="F16" s="2">
+        <v>0</v>
+      </c>
+      <c r="G16" s="2">
         <v>2210</v>
       </c>
-      <c r="H16" s="4">
+      <c r="H16" s="3">
         <f t="shared" si="1"/>
         <v>1.0599520383693046</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17" s="2">
         <v>533</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="2">
         <v>13</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="2">
         <v>547</v>
       </c>
-      <c r="E17" s="4">
+      <c r="E17" s="3">
         <f t="shared" si="0"/>
         <v>1.026266416510319</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="2">
         <v>1306</v>
       </c>
-      <c r="G17" s="3">
+      <c r="G17" s="2">
         <v>588</v>
       </c>
-      <c r="H17" s="4">
+      <c r="H17" s="3">
         <f t="shared" si="1"/>
         <v>1.1031894934333959</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="2">
         <v>3894</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="2">
         <v>341</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="2">
         <v>3711</v>
       </c>
-      <c r="E18" s="4">
+      <c r="E18" s="3">
         <f t="shared" si="0"/>
         <v>0.95300462249614792</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="2">
         <v>109900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="G18" s="2">
         <v>3967</v>
       </c>
-      <c r="H18" s="4">
+      <c r="H18" s="3">
         <f t="shared" si="1"/>
         <v>1.0187467899332305</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B19" s="2">
         <v>502</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="2">
         <v>2</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="2">
         <v>583</v>
       </c>
-      <c r="E19" s="4">
+      <c r="E19" s="3">
         <f t="shared" si="0"/>
         <v>1.1613545816733069</v>
       </c>
-      <c r="F19" s="3">
+      <c r="F19" s="2">
         <v>69</v>
       </c>
-      <c r="G19" s="3">
+      <c r="G19" s="2">
         <v>634</v>
       </c>
-      <c r="H19" s="4">
+      <c r="H19" s="3">
         <f t="shared" si="1"/>
         <v>1.2629482071713147</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B20" s="2">
         <v>21282</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" s="2">
         <v>2</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="2">
         <v>24698</v>
       </c>
-      <c r="E20" s="4">
+      <c r="E20" s="3">
         <f t="shared" si="0"/>
         <v>1.1605112301475424</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="2">
         <v>84</v>
       </c>
-      <c r="G20" s="3">
+      <c r="G20" s="2">
         <v>26442</v>
       </c>
-      <c r="H20" s="4">
+      <c r="H20" s="3">
         <f t="shared" si="1"/>
         <v>1.2424584155624472</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B21" s="2">
         <v>20749</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21" s="2">
         <v>3</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="2">
         <v>23660</v>
       </c>
-      <c r="E21" s="4">
+      <c r="E21" s="3">
         <f t="shared" si="0"/>
         <v>1.1402959178755603</v>
       </c>
-      <c r="F21" s="3">
+      <c r="F21" s="2">
         <v>86</v>
       </c>
-      <c r="G21" s="3">
+      <c r="G21" s="2">
         <v>27130</v>
       </c>
-      <c r="H21" s="4">
+      <c r="H21" s="3">
         <f t="shared" si="1"/>
         <v>1.3075328931514771</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="3">
+      <c r="B22" s="2">
         <v>21294</v>
       </c>
-      <c r="C22" s="3">
+      <c r="C22" s="2">
         <v>3</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="2">
         <v>24852</v>
       </c>
-      <c r="E22" s="4">
+      <c r="E22" s="3">
         <f t="shared" si="0"/>
         <v>1.1670893209354747</v>
       </c>
-      <c r="F22" s="3">
+      <c r="F22" s="2">
         <v>84</v>
       </c>
-      <c r="G22" s="3">
+      <c r="G22" s="2">
         <v>26002</v>
       </c>
-      <c r="H22" s="4">
+      <c r="H22" s="3">
         <f t="shared" si="1"/>
         <v>1.2210951441720672</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B23" s="3">
+      <c r="B23" s="2">
         <v>14379</v>
       </c>
-      <c r="C23" s="3">
+      <c r="C23" s="2">
         <v>3</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="2">
         <v>16935</v>
       </c>
-      <c r="E23" s="4">
+      <c r="E23" s="3">
         <f t="shared" si="0"/>
         <v>1.177759232213645</v>
       </c>
-      <c r="F23" s="3">
+      <c r="F23" s="2">
         <v>100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="G23" s="2">
         <v>18901</v>
       </c>
-      <c r="H23" s="4">
+      <c r="H23" s="3">
         <f t="shared" si="1"/>
         <v>1.3144864037832951</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B24" s="3">
+      <c r="B24" s="2">
         <v>291</v>
       </c>
-      <c r="C24" s="3">
-        <v>0</v>
-      </c>
-      <c r="D24" s="3">
+      <c r="C24" s="2">
+        <v>0</v>
+      </c>
+      <c r="D24" s="2">
         <v>291</v>
       </c>
-      <c r="E24" s="4">
+      <c r="E24" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
+      <c r="F24" s="2">
+        <v>0</v>
+      </c>
+      <c r="G24" s="2">
         <v>299</v>
       </c>
-      <c r="H24" s="4">
+      <c r="H24" s="3">
         <f t="shared" si="1"/>
         <v>1.0274914089347078</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B25" s="3">
+      <c r="B25" s="2">
         <v>19311</v>
       </c>
-      <c r="C25" s="3">
+      <c r="C25" s="2">
         <v>229</v>
       </c>
-      <c r="D25" s="3">
+      <c r="D25" s="2">
         <v>17927</v>
       </c>
-      <c r="E25" s="4">
+      <c r="E25" s="3">
         <f t="shared" si="0"/>
         <v>0.92833100305525351</v>
       </c>
-      <c r="F25" s="3">
+      <c r="F25" s="2">
         <v>70952</v>
       </c>
-      <c r="G25" s="3">
+      <c r="G25" s="2">
         <v>20958</v>
       </c>
-      <c r="H25" s="4">
+      <c r="H25" s="3">
         <f t="shared" si="1"/>
         <v>1.0852881777225416</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B26" s="3">
+      <c r="B26" s="2">
         <v>50778</v>
       </c>
-      <c r="C26" s="3">
+      <c r="C26" s="2">
         <v>132</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="2">
         <v>58950</v>
       </c>
-      <c r="E26" s="4">
+      <c r="E26" s="3">
         <f t="shared" si="0"/>
         <v>1.1609358383551931</v>
       </c>
-      <c r="F26" s="3">
+      <c r="F26" s="2">
         <v>29490</v>
       </c>
-      <c r="G26" s="3">
+      <c r="G26" s="2">
         <v>68397</v>
       </c>
-      <c r="H26" s="4">
+      <c r="H26" s="3">
         <f t="shared" si="1"/>
         <v>1.3469809760132341</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B27" s="3">
+      <c r="B27" s="2">
         <v>259045</v>
       </c>
-      <c r="C27" s="3">
+      <c r="C27" s="2">
         <v>1196</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="2">
         <v>313745</v>
       </c>
-      <c r="E27" s="4">
+      <c r="E27" s="3">
         <f t="shared" si="0"/>
         <v>1.2111602231272558</v>
       </c>
-      <c r="F27" s="3">
+      <c r="F27" s="2">
         <v>502354</v>
       </c>
-      <c r="G27" s="3">
+      <c r="G27" s="2">
         <v>347246</v>
       </c>
-      <c r="H27" s="4">
+      <c r="H27" s="3">
         <f t="shared" si="1"/>
         <v>1.3404852438765464</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B28" s="3">
+      <c r="B28" s="2">
         <v>108159</v>
       </c>
-      <c r="C28" s="3">
+      <c r="C28" s="2">
         <v>1</v>
       </c>
-      <c r="D28" s="3">
+      <c r="D28" s="2">
         <v>130921</v>
       </c>
-      <c r="E28" s="4">
+      <c r="E28" s="3">
         <f t="shared" si="0"/>
         <v>1.2104494309303895</v>
       </c>
-      <c r="F28" s="3">
+      <c r="F28" s="2">
         <v>29</v>
       </c>
-      <c r="G28" s="3">
+      <c r="G28" s="2">
         <v>142085</v>
       </c>
-      <c r="H28" s="4">
+      <c r="H28" s="3">
         <f t="shared" si="1"/>
         <v>1.3136678408639133</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B29" s="3">
+      <c r="B29" s="2">
         <v>7755</v>
       </c>
-      <c r="C29" s="3">
+      <c r="C29" s="2">
         <v>3</v>
       </c>
-      <c r="D29" s="3">
+      <c r="D29" s="2">
         <v>9424</v>
       </c>
-      <c r="E29" s="4">
+      <c r="E29" s="3">
         <f t="shared" si="0"/>
         <v>1.2152159896840748</v>
       </c>
-      <c r="F29" s="3">
+      <c r="F29" s="2">
         <v>84</v>
       </c>
-      <c r="G29" s="3">
+      <c r="G29" s="2">
         <v>10646</v>
       </c>
-      <c r="H29" s="4">
+      <c r="H29" s="3">
         <f t="shared" si="1"/>
         <v>1.3727917472598323</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B30" s="3">
+      <c r="B30" s="2">
         <v>675</v>
       </c>
-      <c r="C30" s="3">
+      <c r="C30" s="2">
         <v>1</v>
       </c>
-      <c r="D30" s="3">
+      <c r="D30" s="2">
         <v>796</v>
       </c>
-      <c r="E30" s="4">
+      <c r="E30" s="3">
         <f t="shared" si="0"/>
         <v>1.1792592592592592</v>
       </c>
-      <c r="F30" s="3">
+      <c r="F30" s="2">
         <v>22</v>
       </c>
-      <c r="G30" s="3">
+      <c r="G30" s="2">
         <v>862</v>
       </c>
-      <c r="H30" s="4">
+      <c r="H30" s="3">
         <f t="shared" si="1"/>
         <v>1.277037037037037</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" s="3" t="s">
+      <c r="A31" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B31" s="3">
+      <c r="B31" s="2">
         <v>3854</v>
       </c>
-      <c r="C31" s="3">
+      <c r="C31" s="2">
         <v>20</v>
       </c>
-      <c r="D31" s="3">
+      <c r="D31" s="2">
         <v>4647</v>
       </c>
-      <c r="E31" s="4">
+      <c r="E31" s="3">
         <f t="shared" si="0"/>
         <v>1.2057602490918526</v>
       </c>
-      <c r="F31" s="3">
+      <c r="F31" s="2">
         <v>1989</v>
       </c>
-      <c r="G31" s="3">
+      <c r="G31" s="2">
         <v>5122</v>
       </c>
-      <c r="H31" s="4">
+      <c r="H31" s="3">
         <f t="shared" si="1"/>
         <v>1.3290088220031135</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B32" s="3">
+      <c r="B32" s="2">
         <v>71</v>
       </c>
-      <c r="C32" s="3">
-        <v>0</v>
-      </c>
-      <c r="D32" s="3">
+      <c r="C32" s="2">
+        <v>0</v>
+      </c>
+      <c r="D32" s="2">
         <v>74</v>
       </c>
-      <c r="E32" s="4">
+      <c r="E32" s="3">
         <f t="shared" si="0"/>
         <v>1.0422535211267605</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
+      <c r="F32" s="2">
+        <v>0</v>
+      </c>
+      <c r="G32" s="2">
         <v>72</v>
       </c>
-      <c r="H32" s="4">
+      <c r="H32" s="3">
         <f t="shared" si="1"/>
         <v>1.0140845070422535</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" s="3" t="s">
+      <c r="A33" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B33" s="3">
+      <c r="B33" s="2">
         <v>73</v>
       </c>
-      <c r="C33" s="3">
-        <v>0</v>
-      </c>
-      <c r="D33" s="3">
+      <c r="C33" s="2">
+        <v>0</v>
+      </c>
+      <c r="D33" s="2">
         <v>86</v>
       </c>
-      <c r="E33" s="4">
+      <c r="E33" s="3">
         <f t="shared" si="0"/>
         <v>1.178082191780822</v>
       </c>
-      <c r="F33" s="3">
+      <c r="F33" s="2">
         <v>2</v>
       </c>
-      <c r="G33" s="3">
+      <c r="G33" s="2">
         <v>75</v>
       </c>
-      <c r="H33" s="4">
+      <c r="H33" s="3">
         <f t="shared" si="1"/>
         <v>1.0273972602739727</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
+      <c r="A34" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B34" s="2"/>
-      <c r="C34" s="5">
+      <c r="B34" s="5"/>
+      <c r="C34" s="6">
         <f>AVERAGE(E3:E33)</f>
         <v>1.11761803703935</v>
       </c>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="5">
+      <c r="D34" s="5"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="6">
         <f>AVERAGE(H3:H33)</f>
         <v>1.2143778281984563</v>
       </c>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/resource/result.xlsx
+++ b/resource/result.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b1fc4107772a6185/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_Files\_Lessons\ALGORITHM\Project\resource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{5BFC3DE5-5D6D-421B-964B-B7DC593EE6E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6B9FAC1-3667-4000-84A6-A9AE6DB45EE1}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14622D44-2112-4698-B9D1-C7263E7E6A14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXACT" sheetId="9" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="50">
   <si>
     <t>att48</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -161,10 +161,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>p15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>pa561</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -230,7 +226,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Average Ratio</t>
+    <t>Average</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ratio</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -612,35 +612,35 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E1" s="5"/>
       <c r="F1" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G1" s="5"/>
       <c r="H1" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I1" s="5"/>
       <c r="J1" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="5"/>
       <c r="B2" s="5"/>
       <c r="C2" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -661,7 +661,7 @@
         <v>6</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -728,7 +728,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B5" s="2">
         <v>71</v>
@@ -785,7 +785,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{260DB66E-1FFD-4D32-BA5D-DB6972467A37}">
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.33203125" style="1" customWidth="1"/>
@@ -795,7 +795,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>4</v>
@@ -835,562 +835,562 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B3" s="2">
-        <v>2579</v>
+        <v>19</v>
       </c>
       <c r="C3" s="2">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D3" s="2">
-        <v>2975</v>
+        <v>21</v>
       </c>
       <c r="E3" s="3">
-        <f>D3/B3</f>
-        <v>1.1535478867778208</v>
+        <f t="shared" ref="E3:E33" si="0">D3/B3</f>
+        <v>1.1052631578947369</v>
       </c>
       <c r="F3" s="2">
-        <v>4514</v>
+        <v>0</v>
       </c>
       <c r="G3" s="2">
-        <v>3313</v>
+        <v>21</v>
       </c>
       <c r="H3" s="3">
-        <f>G3/B3</f>
-        <v>1.2846064366033347</v>
+        <f t="shared" ref="H3:H33" si="1">G3/B3</f>
+        <v>1.1052631578947369</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B4" s="2">
-        <v>33523</v>
+        <v>291</v>
       </c>
       <c r="C4" s="2">
         <v>0</v>
       </c>
       <c r="D4" s="2">
-        <v>37928</v>
+        <v>291</v>
       </c>
       <c r="E4" s="3">
-        <f t="shared" ref="E4:E33" si="0">D4/B4</f>
-        <v>1.1314023207946782</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="F4" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G4" s="2">
-        <v>41190</v>
+        <v>299</v>
       </c>
       <c r="H4" s="3">
-        <f t="shared" ref="H4:H33" si="1">G4/B4</f>
-        <v>1.2287086477940519</v>
+        <f t="shared" si="1"/>
+        <v>1.0274914089347078</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="B5" s="2">
-        <v>9073</v>
+        <v>71</v>
       </c>
       <c r="C5" s="2">
         <v>0</v>
       </c>
       <c r="D5" s="2">
-        <v>9962</v>
+        <v>74</v>
       </c>
       <c r="E5" s="3">
         <f t="shared" si="0"/>
-        <v>1.0979830265623278</v>
+        <v>1.0422535211267605</v>
       </c>
       <c r="F5" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G5" s="2">
-        <v>10341</v>
+        <v>72</v>
       </c>
       <c r="H5" s="3">
         <f t="shared" si="1"/>
-        <v>1.1397553179764135</v>
+        <v>1.0140845070422535</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B6" s="2">
-        <v>9290</v>
+        <v>2085</v>
       </c>
       <c r="C6" s="2">
         <v>0</v>
       </c>
       <c r="D6" s="2">
-        <v>9962</v>
+        <v>2178</v>
       </c>
       <c r="E6" s="3">
         <f t="shared" si="0"/>
-        <v>1.0723358449946179</v>
+        <v>1.0446043165467627</v>
       </c>
       <c r="F6" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="2">
-        <v>10341</v>
+        <v>2210</v>
       </c>
       <c r="H6" s="3">
         <f t="shared" si="1"/>
-        <v>1.1131324004305705</v>
+        <v>1.0599520383693046</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="B7" s="2">
-        <v>7542</v>
+        <v>73</v>
       </c>
       <c r="C7" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" s="2">
-        <v>8181</v>
+        <v>86</v>
       </c>
       <c r="E7" s="3">
         <f t="shared" si="0"/>
-        <v>1.0847255369928401</v>
+        <v>1.178082191780822</v>
       </c>
       <c r="F7" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G7" s="2">
-        <v>9550</v>
+        <v>75</v>
       </c>
       <c r="H7" s="3">
         <f t="shared" si="1"/>
-        <v>1.2662423760275789</v>
+        <v>1.0273972602739727</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B8" s="2">
-        <v>6105</v>
+        <v>937</v>
       </c>
       <c r="C8" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D8" s="2">
-        <v>7049</v>
+        <v>965</v>
       </c>
       <c r="E8" s="3">
         <f t="shared" si="0"/>
-        <v>1.1546273546273547</v>
+        <v>1.0298826040554963</v>
       </c>
       <c r="F8" s="2">
-        <v>234</v>
+        <v>0</v>
       </c>
       <c r="G8" s="2">
-        <v>7906</v>
+        <v>1102</v>
       </c>
       <c r="H8" s="3">
         <f t="shared" si="1"/>
-        <v>1.2950040950040951</v>
+        <v>1.176093916755603</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B9" s="2">
-        <v>6527</v>
+        <v>9073</v>
       </c>
       <c r="C9" s="2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D9" s="2">
-        <v>7213</v>
+        <v>9962</v>
       </c>
       <c r="E9" s="3">
         <f t="shared" si="0"/>
-        <v>1.105101884479853</v>
+        <v>1.0979830265623278</v>
       </c>
       <c r="F9" s="2">
-        <v>416</v>
+        <v>2</v>
       </c>
       <c r="G9" s="2">
-        <v>8140</v>
+        <v>10341</v>
       </c>
       <c r="H9" s="3">
         <f t="shared" si="1"/>
-        <v>1.24712731729738</v>
+        <v>1.1397553179764135</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B10" s="2">
-        <v>629</v>
+        <v>9290</v>
       </c>
       <c r="C10" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D10" s="2">
-        <v>746</v>
+        <v>9962</v>
       </c>
       <c r="E10" s="3">
         <f t="shared" si="0"/>
-        <v>1.1860095389507155</v>
+        <v>1.0723358449946179</v>
       </c>
       <c r="F10" s="2">
-        <v>85</v>
+        <v>1</v>
       </c>
       <c r="G10" s="2">
-        <v>822</v>
+        <v>10341</v>
       </c>
       <c r="H10" s="3">
         <f t="shared" si="1"/>
-        <v>1.3068362480127187</v>
+        <v>1.1131324004305705</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="B11" s="2">
-        <v>426</v>
+        <v>33523</v>
       </c>
       <c r="C11" s="2">
         <v>0</v>
       </c>
       <c r="D11" s="2">
-        <v>482</v>
+        <v>37928</v>
       </c>
       <c r="E11" s="3">
         <f t="shared" si="0"/>
-        <v>1.1314553990610328</v>
+        <v>1.1314023207946782</v>
       </c>
       <c r="F11" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G11" s="2">
-        <v>556</v>
+        <v>41190</v>
       </c>
       <c r="H11" s="3">
         <f t="shared" si="1"/>
-        <v>1.3051643192488263</v>
+        <v>1.2287086477940519</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" s="2">
-        <v>538</v>
+        <v>426</v>
       </c>
       <c r="C12" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" s="2">
-        <v>608</v>
+        <v>482</v>
       </c>
       <c r="E12" s="3">
         <f t="shared" si="0"/>
-        <v>1.1301115241635689</v>
+        <v>1.1314553990610328</v>
       </c>
       <c r="F12" s="2">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="G12" s="2">
-        <v>674</v>
+        <v>556</v>
       </c>
       <c r="H12" s="3">
         <f t="shared" si="1"/>
-        <v>1.2527881040892193</v>
+        <v>1.3051643192488263</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B13" s="2">
-        <v>19</v>
+        <v>7542</v>
       </c>
       <c r="C13" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" s="2">
-        <v>21</v>
+        <v>8181</v>
       </c>
       <c r="E13" s="3">
         <f t="shared" si="0"/>
-        <v>1.1052631578947369</v>
+        <v>1.0847255369928401</v>
       </c>
       <c r="F13" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G13" s="2">
-        <v>21</v>
+        <v>9550</v>
       </c>
       <c r="H13" s="3">
         <f t="shared" si="1"/>
-        <v>1.1052631578947369</v>
+        <v>1.2662423760275789</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="B14" s="2">
-        <v>937</v>
+        <v>675</v>
       </c>
       <c r="C14" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" s="2">
-        <v>965</v>
+        <v>796</v>
       </c>
       <c r="E14" s="3">
         <f t="shared" si="0"/>
-        <v>1.0298826040554963</v>
+        <v>1.1792592592592592</v>
       </c>
       <c r="F14" s="2">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G14" s="2">
-        <v>1102</v>
+        <v>862</v>
       </c>
       <c r="H14" s="3">
         <f t="shared" si="1"/>
-        <v>1.176093916755603</v>
+        <v>1.277037037037037</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B15" s="2">
-        <v>1667</v>
+        <v>538</v>
       </c>
       <c r="C15" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D15" s="2">
-        <v>1836</v>
+        <v>608</v>
       </c>
       <c r="E15" s="3">
         <f t="shared" si="0"/>
-        <v>1.101379724055189</v>
+        <v>1.1301115241635689</v>
       </c>
       <c r="F15" s="2">
-        <v>169</v>
+        <v>29</v>
       </c>
       <c r="G15" s="2">
-        <v>2101</v>
+        <v>674</v>
       </c>
       <c r="H15" s="3">
         <f t="shared" si="1"/>
-        <v>1.2603479304139171</v>
+        <v>1.2527881040892193</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="B16" s="2">
-        <v>2085</v>
+        <v>108159</v>
       </c>
       <c r="C16" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16" s="2">
-        <v>2178</v>
+        <v>130921</v>
       </c>
       <c r="E16" s="3">
         <f t="shared" si="0"/>
-        <v>1.0446043165467627</v>
+        <v>1.2104494309303895</v>
       </c>
       <c r="F16" s="2">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G16" s="2">
-        <v>2210</v>
+        <v>142085</v>
       </c>
       <c r="H16" s="3">
         <f t="shared" si="1"/>
-        <v>1.0599520383693046</v>
+        <v>1.3136678408639133</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B17" s="2">
-        <v>533</v>
+        <v>502</v>
       </c>
       <c r="C17" s="2">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D17" s="2">
-        <v>547</v>
+        <v>583</v>
       </c>
       <c r="E17" s="3">
         <f t="shared" si="0"/>
-        <v>1.026266416510319</v>
+        <v>1.1613545816733069</v>
       </c>
       <c r="F17" s="2">
-        <v>1306</v>
+        <v>69</v>
       </c>
       <c r="G17" s="2">
-        <v>588</v>
+        <v>634</v>
       </c>
       <c r="H17" s="3">
         <f t="shared" si="1"/>
-        <v>1.1031894934333959</v>
+        <v>1.2629482071713147</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B18" s="2">
-        <v>3894</v>
+        <v>21282</v>
       </c>
       <c r="C18" s="2">
-        <v>341</v>
+        <v>2</v>
       </c>
       <c r="D18" s="2">
-        <v>3711</v>
+        <v>24698</v>
       </c>
       <c r="E18" s="3">
         <f t="shared" si="0"/>
-        <v>0.95300462249614792</v>
+        <v>1.1605112301475424</v>
       </c>
       <c r="F18" s="2">
-        <v>109900</v>
+        <v>84</v>
       </c>
       <c r="G18" s="2">
-        <v>3967</v>
+        <v>26442</v>
       </c>
       <c r="H18" s="3">
         <f t="shared" si="1"/>
-        <v>1.0187467899332305</v>
+        <v>1.2424584155624472</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B19" s="2">
-        <v>502</v>
+        <v>20749</v>
       </c>
       <c r="C19" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D19" s="2">
-        <v>583</v>
+        <v>23660</v>
       </c>
       <c r="E19" s="3">
         <f t="shared" si="0"/>
-        <v>1.1613545816733069</v>
+        <v>1.1402959178755603</v>
       </c>
       <c r="F19" s="2">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="G19" s="2">
-        <v>634</v>
+        <v>27130</v>
       </c>
       <c r="H19" s="3">
         <f t="shared" si="1"/>
-        <v>1.2629482071713147</v>
+        <v>1.3075328931514771</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B20" s="2">
-        <v>21282</v>
+        <v>21294</v>
       </c>
       <c r="C20" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D20" s="2">
-        <v>24698</v>
+        <v>24852</v>
       </c>
       <c r="E20" s="3">
         <f t="shared" si="0"/>
-        <v>1.1605112301475424</v>
+        <v>1.1670893209354747</v>
       </c>
       <c r="F20" s="2">
         <v>84</v>
       </c>
       <c r="G20" s="2">
-        <v>26442</v>
+        <v>26002</v>
       </c>
       <c r="H20" s="3">
         <f t="shared" si="1"/>
-        <v>1.2424584155624472</v>
+        <v>1.2210951441720672</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="B21" s="2">
-        <v>20749</v>
+        <v>7755</v>
       </c>
       <c r="C21" s="2">
         <v>3</v>
       </c>
       <c r="D21" s="2">
-        <v>23660</v>
+        <v>9424</v>
       </c>
       <c r="E21" s="3">
         <f t="shared" si="0"/>
-        <v>1.1402959178755603</v>
+        <v>1.2152159896840748</v>
       </c>
       <c r="F21" s="2">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G21" s="2">
-        <v>27130</v>
+        <v>10646</v>
       </c>
       <c r="H21" s="3">
         <f t="shared" si="1"/>
-        <v>1.3075328931514771</v>
+        <v>1.3727917472598323</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B22" s="2">
-        <v>21294</v>
+        <v>629</v>
       </c>
       <c r="C22" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D22" s="2">
-        <v>24852</v>
+        <v>746</v>
       </c>
       <c r="E22" s="3">
         <f t="shared" si="0"/>
-        <v>1.1670893209354747</v>
+        <v>1.1860095389507155</v>
       </c>
       <c r="F22" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G22" s="2">
-        <v>26002</v>
+        <v>822</v>
       </c>
       <c r="H22" s="3">
         <f t="shared" si="1"/>
-        <v>1.2210951441720672</v>
+        <v>1.3068362480127187</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
@@ -1423,311 +1423,336 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="B24" s="2">
-        <v>291</v>
+        <v>1667</v>
       </c>
       <c r="C24" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D24" s="2">
-        <v>291</v>
+        <v>1836</v>
       </c>
       <c r="E24" s="3">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>1.101379724055189</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="G24" s="2">
-        <v>299</v>
+        <v>2101</v>
       </c>
       <c r="H24" s="3">
         <f t="shared" si="1"/>
-        <v>1.0274914089347078</v>
+        <v>1.2603479304139171</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="B25" s="2">
-        <v>19311</v>
+        <v>6105</v>
       </c>
       <c r="C25" s="2">
-        <v>229</v>
+        <v>5</v>
       </c>
       <c r="D25" s="2">
-        <v>17927</v>
+        <v>7049</v>
       </c>
       <c r="E25" s="3">
         <f t="shared" si="0"/>
-        <v>0.92833100305525351</v>
+        <v>1.1546273546273547</v>
       </c>
       <c r="F25" s="2">
-        <v>70952</v>
+        <v>234</v>
       </c>
       <c r="G25" s="2">
-        <v>20958</v>
+        <v>7906</v>
       </c>
       <c r="H25" s="3">
         <f t="shared" si="1"/>
-        <v>1.0852881777225416</v>
+        <v>1.2950040950040951</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="B26" s="2">
-        <v>50778</v>
+        <v>6527</v>
       </c>
       <c r="C26" s="2">
-        <v>132</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2">
-        <v>58950</v>
+        <v>7213</v>
       </c>
       <c r="E26" s="3">
         <f t="shared" si="0"/>
-        <v>1.1609358383551931</v>
+        <v>1.105101884479853</v>
       </c>
       <c r="F26" s="2">
-        <v>29490</v>
+        <v>416</v>
       </c>
       <c r="G26" s="2">
-        <v>68397</v>
+        <v>8140</v>
       </c>
       <c r="H26" s="3">
         <f t="shared" si="1"/>
-        <v>1.3469809760132341</v>
+        <v>1.24712731729738</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="B27" s="2">
-        <v>259045</v>
+        <v>533</v>
       </c>
       <c r="C27" s="2">
-        <v>1196</v>
+        <v>13</v>
       </c>
       <c r="D27" s="2">
-        <v>313745</v>
+        <v>547</v>
       </c>
       <c r="E27" s="3">
         <f t="shared" si="0"/>
-        <v>1.2111602231272558</v>
+        <v>1.026266416510319</v>
       </c>
       <c r="F27" s="2">
-        <v>502354</v>
+        <v>1306</v>
       </c>
       <c r="G27" s="2">
-        <v>347246</v>
+        <v>588</v>
       </c>
       <c r="H27" s="3">
         <f t="shared" si="1"/>
-        <v>1.3404852438765464</v>
+        <v>1.1031894934333959</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B28" s="2">
-        <v>108159</v>
+        <v>3854</v>
       </c>
       <c r="C28" s="2">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D28" s="2">
-        <v>130921</v>
+        <v>4647</v>
       </c>
       <c r="E28" s="3">
         <f t="shared" si="0"/>
-        <v>1.2104494309303895</v>
+        <v>1.2057602490918526</v>
       </c>
       <c r="F28" s="2">
-        <v>29</v>
+        <v>1989</v>
       </c>
       <c r="G28" s="2">
-        <v>142085</v>
+        <v>5122</v>
       </c>
       <c r="H28" s="3">
         <f t="shared" si="1"/>
-        <v>1.3136678408639133</v>
+        <v>1.3290088220031135</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="B29" s="2">
-        <v>7755</v>
+        <v>2579</v>
       </c>
       <c r="C29" s="2">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="D29" s="2">
-        <v>9424</v>
+        <v>2975</v>
       </c>
       <c r="E29" s="3">
         <f t="shared" si="0"/>
-        <v>1.2152159896840748</v>
+        <v>1.1535478867778208</v>
       </c>
       <c r="F29" s="2">
-        <v>84</v>
+        <v>4514</v>
       </c>
       <c r="G29" s="2">
-        <v>10646</v>
+        <v>3313</v>
       </c>
       <c r="H29" s="3">
         <f t="shared" si="1"/>
-        <v>1.3727917472598323</v>
+        <v>1.2846064366033347</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B30" s="2">
-        <v>675</v>
+        <v>50778</v>
       </c>
       <c r="C30" s="2">
-        <v>1</v>
+        <v>132</v>
       </c>
       <c r="D30" s="2">
-        <v>796</v>
+        <v>58950</v>
       </c>
       <c r="E30" s="3">
         <f t="shared" si="0"/>
-        <v>1.1792592592592592</v>
+        <v>1.1609358383551931</v>
       </c>
       <c r="F30" s="2">
-        <v>22</v>
+        <v>29490</v>
       </c>
       <c r="G30" s="2">
-        <v>862</v>
+        <v>68397</v>
       </c>
       <c r="H30" s="3">
         <f t="shared" si="1"/>
-        <v>1.277037037037037</v>
+        <v>1.3469809760132341</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="B31" s="2">
-        <v>3854</v>
+        <v>19311</v>
       </c>
       <c r="C31" s="2">
-        <v>20</v>
+        <v>229</v>
       </c>
       <c r="D31" s="2">
-        <v>4647</v>
+        <v>17927</v>
       </c>
       <c r="E31" s="3">
         <f t="shared" si="0"/>
-        <v>1.2057602490918526</v>
+        <v>0.92833100305525351</v>
       </c>
       <c r="F31" s="2">
-        <v>1989</v>
+        <v>70952</v>
       </c>
       <c r="G31" s="2">
-        <v>5122</v>
+        <v>20958</v>
       </c>
       <c r="H31" s="3">
         <f t="shared" si="1"/>
-        <v>1.3290088220031135</v>
+        <v>1.0852881777225416</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="B32" s="2">
-        <v>71</v>
+        <v>3894</v>
       </c>
       <c r="C32" s="2">
-        <v>0</v>
+        <v>341</v>
       </c>
       <c r="D32" s="2">
-        <v>74</v>
+        <v>3711</v>
       </c>
       <c r="E32" s="3">
         <f t="shared" si="0"/>
-        <v>1.0422535211267605</v>
+        <v>0.95300462249614792</v>
       </c>
       <c r="F32" s="2">
-        <v>0</v>
+        <v>109900</v>
       </c>
       <c r="G32" s="2">
-        <v>72</v>
+        <v>3967</v>
       </c>
       <c r="H32" s="3">
         <f t="shared" si="1"/>
-        <v>1.0140845070422535</v>
+        <v>1.0187467899332305</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="B33" s="2">
-        <v>73</v>
+        <v>259045</v>
       </c>
       <c r="C33" s="2">
-        <v>0</v>
+        <v>1196</v>
       </c>
       <c r="D33" s="2">
-        <v>86</v>
+        <v>313745</v>
       </c>
       <c r="E33" s="3">
         <f t="shared" si="0"/>
-        <v>1.178082191780822</v>
+        <v>1.2111602231272558</v>
       </c>
       <c r="F33" s="2">
-        <v>2</v>
+        <v>502354</v>
       </c>
       <c r="G33" s="2">
-        <v>75</v>
+        <v>347246</v>
       </c>
       <c r="H33" s="3">
         <f t="shared" si="1"/>
-        <v>1.0273972602739727</v>
+        <v>1.3404852438765464</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B34" s="5"/>
+        <v>48</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>5</v>
+      </c>
       <c r="C34" s="6">
-        <f>AVERAGE(E3:E33)</f>
-        <v>1.11761803703935</v>
+        <f>AVERAGE(C3:C33)</f>
+        <v>64.645161290322577</v>
       </c>
       <c r="D34" s="5"/>
       <c r="E34" s="5"/>
       <c r="F34" s="6">
-        <f>AVERAGE(H3:H33)</f>
-        <v>1.2143778281984563</v>
+        <f>AVERAGE(F3:F33)</f>
+        <v>23291.032258064515</v>
       </c>
       <c r="G34" s="5"/>
       <c r="H34" s="5"/>
     </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A35" s="5"/>
+      <c r="B35" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C35" s="6">
+        <f>AVERAGE(E4:E34)</f>
+        <v>1.1180298663441703</v>
+      </c>
+      <c r="D35" s="5"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="6">
+        <f>AVERAGE(H4:H34)</f>
+        <v>1.2180149838752463</v>
+      </c>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
+    </row>
   </sheetData>
-  <mergeCells count="7">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:H33">
+    <sortCondition ref="F3:F33"/>
+  </sortState>
+  <mergeCells count="9">
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A34:B34"/>
     <mergeCell ref="C34:E34"/>
     <mergeCell ref="F34:H34"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="F35:H35"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/resource/result.xlsx
+++ b/resource/result.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_Files\_Lessons\ALGORITHM\Project\resource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14622D44-2112-4698-B9D1-C7263E7E6A14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B51F813-F251-46DF-93E0-3CF12D1D0C85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5130" yWindow="2760" windowWidth="19200" windowHeight="11170" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXACT" sheetId="9" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="48">
   <si>
     <t>att48</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -137,10 +137,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>gr666</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>gr96</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -158,10 +154,6 @@
   </si>
   <si>
     <t>lin105</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>pa561</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -612,35 +604,35 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E1" s="5"/>
       <c r="F1" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G1" s="5"/>
       <c r="H1" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I1" s="5"/>
       <c r="J1" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="5"/>
       <c r="B2" s="5"/>
       <c r="C2" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -661,7 +653,7 @@
         <v>6</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -728,7 +720,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B5" s="2">
         <v>71</v>
@@ -785,7 +777,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{260DB66E-1FFD-4D32-BA5D-DB6972467A37}">
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.33203125" style="1" customWidth="1"/>
@@ -795,7 +787,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>4</v>
@@ -847,7 +839,7 @@
         <v>21</v>
       </c>
       <c r="E3" s="3">
-        <f t="shared" ref="E3:E33" si="0">D3/B3</f>
+        <f t="shared" ref="E3:E31" si="0">D3/B3</f>
         <v>1.1052631578947369</v>
       </c>
       <c r="F3" s="2">
@@ -857,7 +849,7 @@
         <v>21</v>
       </c>
       <c r="H3" s="3">
-        <f t="shared" ref="H3:H33" si="1">G3/B3</f>
+        <f t="shared" ref="H3:H31" si="1">G3/B3</f>
         <v>1.1052631578947369</v>
       </c>
     </row>
@@ -891,7 +883,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B5" s="2">
         <v>71</v>
@@ -947,7 +939,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B7" s="2">
         <v>73</v>
@@ -1143,7 +1135,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B14" s="2">
         <v>675</v>
@@ -1199,7 +1191,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B16" s="2">
         <v>108159</v>
@@ -1227,7 +1219,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B17" s="2">
         <v>502</v>
@@ -1255,7 +1247,7 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B18" s="2">
         <v>21282</v>
@@ -1283,7 +1275,7 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B19" s="2">
         <v>20749</v>
@@ -1311,7 +1303,7 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B20" s="2">
         <v>21294</v>
@@ -1339,7 +1331,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B21" s="2">
         <v>7755</v>
@@ -1395,7 +1387,7 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B23" s="2">
         <v>14379</v>
@@ -1535,7 +1527,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B28" s="2">
         <v>3854</v>
@@ -1591,7 +1583,7 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B30" s="2">
         <v>50778</v>
@@ -1622,137 +1614,81 @@
         <v>31</v>
       </c>
       <c r="B31" s="2">
-        <v>19311</v>
+        <v>259045</v>
       </c>
       <c r="C31" s="2">
-        <v>229</v>
+        <v>1196</v>
       </c>
       <c r="D31" s="2">
-        <v>17927</v>
+        <v>313745</v>
       </c>
       <c r="E31" s="3">
         <f t="shared" si="0"/>
-        <v>0.92833100305525351</v>
+        <v>1.2111602231272558</v>
       </c>
       <c r="F31" s="2">
-        <v>70952</v>
+        <v>502354</v>
       </c>
       <c r="G31" s="2">
-        <v>20958</v>
+        <v>347246</v>
       </c>
       <c r="H31" s="3">
         <f t="shared" si="1"/>
-        <v>1.0852881777225416</v>
+        <v>1.3404852438765464</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B32" s="2">
-        <v>3894</v>
-      </c>
-      <c r="C32" s="2">
-        <v>341</v>
-      </c>
-      <c r="D32" s="2">
-        <v>3711</v>
-      </c>
-      <c r="E32" s="3">
-        <f t="shared" si="0"/>
-        <v>0.95300462249614792</v>
-      </c>
-      <c r="F32" s="2">
-        <v>109900</v>
-      </c>
-      <c r="G32" s="2">
-        <v>3967</v>
-      </c>
-      <c r="H32" s="3">
-        <f t="shared" si="1"/>
-        <v>1.0187467899332305</v>
-      </c>
+      <c r="A32" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C32" s="6">
+        <f>AVERAGE(C3:C31)</f>
+        <v>49.448275862068968</v>
+      </c>
+      <c r="D32" s="5"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="6">
+        <f>AVERAGE(F3:F31)</f>
+        <v>18661.03448275862</v>
+      </c>
+      <c r="G32" s="5"/>
+      <c r="H32" s="5"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B33" s="2">
-        <v>259045</v>
-      </c>
-      <c r="C33" s="2">
-        <v>1196</v>
-      </c>
-      <c r="D33" s="2">
-        <v>313745</v>
-      </c>
-      <c r="E33" s="3">
-        <f t="shared" si="0"/>
-        <v>1.2111602231272558</v>
-      </c>
-      <c r="F33" s="2">
-        <v>502354</v>
-      </c>
-      <c r="G33" s="2">
-        <v>347246</v>
-      </c>
-      <c r="H33" s="3">
-        <f t="shared" si="1"/>
-        <v>1.3404852438765464</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C34" s="6">
-        <f>AVERAGE(C3:C33)</f>
-        <v>64.645161290322577</v>
-      </c>
-      <c r="D34" s="5"/>
-      <c r="E34" s="5"/>
-      <c r="F34" s="6">
-        <f>AVERAGE(F3:F33)</f>
-        <v>23291.032258064515</v>
-      </c>
-      <c r="G34" s="5"/>
-      <c r="H34" s="5"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" s="5"/>
-      <c r="B35" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C35" s="6">
-        <f>AVERAGE(E4:E34)</f>
-        <v>1.1180298663441703</v>
-      </c>
-      <c r="D35" s="5"/>
-      <c r="E35" s="5"/>
-      <c r="F35" s="6">
-        <f>AVERAGE(H4:H34)</f>
-        <v>1.2180149838752463</v>
-      </c>
-      <c r="G35" s="5"/>
-      <c r="H35" s="5"/>
+      <c r="A33" s="5"/>
+      <c r="B33" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C33" s="6">
+        <f>AVERAGE(E4:E32)</f>
+        <v>1.1306985844562039</v>
+      </c>
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="6">
+        <f>AVERAGE(H4:H32)</f>
+        <v>1.2298719481643434</v>
+      </c>
+      <c r="G33" s="5"/>
+      <c r="H33" s="5"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:H33">
-    <sortCondition ref="F3:F33"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:H31">
+    <sortCondition ref="F3:F31"/>
   </sortState>
   <mergeCells count="9">
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A1:A2"/>
-    <mergeCell ref="C34:E34"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="C35:E35"/>
-    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="F33:H33"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/resource/result.xlsx
+++ b/resource/result.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_Files\_Lessons\ALGORITHM\Project\resource\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b1fc4107772a6185/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B51F813-F251-46DF-93E0-3CF12D1D0C85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="76" documentId="13_ncr:1_{8B51F813-F251-46DF-93E0-3CF12D1D0C85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB39C917-9143-4A67-8FA2-9A11F43B6787}"/>
   <bookViews>
-    <workbookView xWindow="5130" yWindow="2760" windowWidth="19200" windowHeight="11170" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXACT" sheetId="9" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="49">
   <si>
     <t>att48</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -77,10 +77,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>MST</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>a280</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -223,6 +219,14 @@
   </si>
   <si>
     <t>Ratio</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MST-0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MST-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -284,7 +288,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -302,6 +306,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -604,35 +611,35 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E1" s="5"/>
       <c r="F1" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G1" s="5"/>
       <c r="H1" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I1" s="5"/>
       <c r="J1" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="5"/>
       <c r="B2" s="5"/>
       <c r="C2" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -653,7 +660,7 @@
         <v>6</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -720,7 +727,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B5" s="2">
         <v>71</v>
@@ -777,7 +784,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{260DB66E-1FFD-4D32-BA5D-DB6972467A37}">
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.33203125" style="1" customWidth="1"/>
@@ -785,9 +792,9 @@
     <col min="3" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>4</v>
@@ -798,12 +805,17 @@
       <c r="D1" s="5"/>
       <c r="E1" s="5"/>
       <c r="F1" s="5" t="s">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I1" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="5"/>
       <c r="B2" s="5"/>
       <c r="C2" s="2" t="s">
@@ -824,10 +836,19 @@
       <c r="H2" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B3" s="2">
         <v>19</v>
@@ -852,8 +873,18 @@
         <f t="shared" ref="H3:H31" si="1">G3/B3</f>
         <v>1.1052631578947369</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I3" s="1">
+        <v>0</v>
+      </c>
+      <c r="J3" s="1">
+        <v>23</v>
+      </c>
+      <c r="K3" s="7">
+        <f>J3/B3</f>
+        <v>1.2105263157894737</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
@@ -880,10 +911,20 @@
         <f t="shared" si="1"/>
         <v>1.0274914089347078</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I4" s="1">
+        <v>0</v>
+      </c>
+      <c r="J4" s="1">
+        <v>291</v>
+      </c>
+      <c r="K4" s="7">
+        <f t="shared" ref="K4:K31" si="2">J4/B4</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B5" s="2">
         <v>71</v>
@@ -908,10 +949,20 @@
         <f t="shared" si="1"/>
         <v>1.0140845070422535</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I5" s="1">
+        <v>0</v>
+      </c>
+      <c r="J5" s="1">
+        <v>79</v>
+      </c>
+      <c r="K5" s="7">
+        <f t="shared" si="2"/>
+        <v>1.1126760563380282</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B6" s="2">
         <v>2085</v>
@@ -936,10 +987,20 @@
         <f t="shared" si="1"/>
         <v>1.0599520383693046</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I6" s="1">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1">
+        <v>2352</v>
+      </c>
+      <c r="K6" s="7">
+        <f t="shared" si="2"/>
+        <v>1.1280575539568345</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B7" s="2">
         <v>73</v>
@@ -964,10 +1025,20 @@
         <f t="shared" si="1"/>
         <v>1.0273972602739727</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I7" s="1">
+        <v>0</v>
+      </c>
+      <c r="J7" s="1">
+        <v>83</v>
+      </c>
+      <c r="K7" s="7">
+        <f t="shared" si="2"/>
+        <v>1.1369863013698631</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B8" s="2">
         <v>937</v>
@@ -992,10 +1063,20 @@
         <f t="shared" si="1"/>
         <v>1.176093916755603</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I8" s="1">
+        <v>0</v>
+      </c>
+      <c r="J8" s="1">
+        <v>1112</v>
+      </c>
+      <c r="K8" s="7">
+        <f t="shared" si="2"/>
+        <v>1.1867662753468518</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" s="2">
         <v>9073</v>
@@ -1020,10 +1101,20 @@
         <f t="shared" si="1"/>
         <v>1.1397553179764135</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I9" s="1">
+        <v>0</v>
+      </c>
+      <c r="J9" s="1">
+        <v>11812</v>
+      </c>
+      <c r="K9" s="7">
+        <f t="shared" si="2"/>
+        <v>1.3018847128843822</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" s="2">
         <v>9290</v>
@@ -1048,8 +1139,18 @@
         <f t="shared" si="1"/>
         <v>1.1131324004305705</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I10" s="1">
+        <v>0</v>
+      </c>
+      <c r="J10" s="1">
+        <v>11812</v>
+      </c>
+      <c r="K10" s="7">
+        <f t="shared" si="2"/>
+        <v>1.2714747039827772</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>0</v>
       </c>
@@ -1076,10 +1177,20 @@
         <f t="shared" si="1"/>
         <v>1.2287086477940519</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I11" s="1">
+        <v>0</v>
+      </c>
+      <c r="J11" s="1">
+        <v>43974</v>
+      </c>
+      <c r="K11" s="7">
+        <f t="shared" si="2"/>
+        <v>1.31175610774692</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12" s="2">
         <v>426</v>
@@ -1104,10 +1215,20 @@
         <f t="shared" si="1"/>
         <v>1.3051643192488263</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I12" s="1">
+        <v>0</v>
+      </c>
+      <c r="J12" s="1">
+        <v>581</v>
+      </c>
+      <c r="K12" s="7">
+        <f t="shared" si="2"/>
+        <v>1.363849765258216</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B13" s="2">
         <v>7542</v>
@@ -1132,10 +1253,20 @@
         <f t="shared" si="1"/>
         <v>1.2662423760275789</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I13" s="1">
+        <v>0</v>
+      </c>
+      <c r="J13" s="1">
+        <v>10114</v>
+      </c>
+      <c r="K13" s="7">
+        <f t="shared" si="2"/>
+        <v>1.3410236011667993</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B14" s="2">
         <v>675</v>
@@ -1160,10 +1291,20 @@
         <f t="shared" si="1"/>
         <v>1.277037037037037</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I14" s="1">
+        <v>0</v>
+      </c>
+      <c r="J14" s="1">
+        <v>888</v>
+      </c>
+      <c r="K14" s="7">
+        <f t="shared" si="2"/>
+        <v>1.3155555555555556</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B15" s="2">
         <v>538</v>
@@ -1188,10 +1329,20 @@
         <f t="shared" si="1"/>
         <v>1.2527881040892193</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I15" s="1">
+        <v>0</v>
+      </c>
+      <c r="J15" s="1">
+        <v>711</v>
+      </c>
+      <c r="K15" s="7">
+        <f t="shared" si="2"/>
+        <v>1.3215613382899629</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B16" s="2">
         <v>108159</v>
@@ -1216,10 +1367,20 @@
         <f t="shared" si="1"/>
         <v>1.3136678408639133</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I16" s="1">
+        <v>0</v>
+      </c>
+      <c r="J16" s="1">
+        <v>145336</v>
+      </c>
+      <c r="K16" s="7">
+        <f t="shared" si="2"/>
+        <v>1.3437254412485322</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B17" s="2">
         <v>502</v>
@@ -1244,10 +1405,20 @@
         <f t="shared" si="1"/>
         <v>1.2629482071713147</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I17" s="1">
+        <v>0</v>
+      </c>
+      <c r="J17" s="1">
+        <v>666</v>
+      </c>
+      <c r="K17" s="7">
+        <f t="shared" si="2"/>
+        <v>1.3266932270916334</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B18" s="2">
         <v>21282</v>
@@ -1272,10 +1443,20 @@
         <f t="shared" si="1"/>
         <v>1.2424584155624472</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I18" s="1">
+        <v>0</v>
+      </c>
+      <c r="J18" s="1">
+        <v>27210</v>
+      </c>
+      <c r="K18" s="7">
+        <f t="shared" si="2"/>
+        <v>1.2785452495066254</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B19" s="2">
         <v>20749</v>
@@ -1300,10 +1481,20 @@
         <f t="shared" si="1"/>
         <v>1.3075328931514771</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I19" s="1">
+        <v>0</v>
+      </c>
+      <c r="J19" s="1">
+        <v>27968</v>
+      </c>
+      <c r="K19" s="7">
+        <f t="shared" si="2"/>
+        <v>1.3479203817051424</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B20" s="2">
         <v>21294</v>
@@ -1328,10 +1519,20 @@
         <f t="shared" si="1"/>
         <v>1.2210951441720672</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I20" s="1">
+        <v>0</v>
+      </c>
+      <c r="J20" s="1">
+        <v>27112</v>
+      </c>
+      <c r="K20" s="7">
+        <f t="shared" si="2"/>
+        <v>1.2732225039917349</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B21" s="2">
         <v>7755</v>
@@ -1356,10 +1557,20 @@
         <f t="shared" si="1"/>
         <v>1.3727917472598323</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I21" s="1">
+        <v>0</v>
+      </c>
+      <c r="J21" s="1">
+        <v>10796</v>
+      </c>
+      <c r="K21" s="7">
+        <f t="shared" si="2"/>
+        <v>1.392134107027724</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B22" s="2">
         <v>629</v>
@@ -1384,10 +1595,20 @@
         <f t="shared" si="1"/>
         <v>1.3068362480127187</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I22" s="1">
+        <v>0</v>
+      </c>
+      <c r="J22" s="1">
+        <v>855</v>
+      </c>
+      <c r="K22" s="7">
+        <f t="shared" si="2"/>
+        <v>1.3593004769475359</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B23" s="2">
         <v>14379</v>
@@ -1412,10 +1633,20 @@
         <f t="shared" si="1"/>
         <v>1.3144864037832951</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I23" s="1">
+        <v>0</v>
+      </c>
+      <c r="J23" s="1">
+        <v>19623</v>
+      </c>
+      <c r="K23" s="7">
+        <f t="shared" si="2"/>
+        <v>1.3646985186730649</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B24" s="2">
         <v>1667</v>
@@ -1440,10 +1671,20 @@
         <f t="shared" si="1"/>
         <v>1.2603479304139171</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I24" s="1">
+        <v>0</v>
+      </c>
+      <c r="J24" s="1">
+        <v>2149</v>
+      </c>
+      <c r="K24" s="7">
+        <f t="shared" si="2"/>
+        <v>1.2891421715656868</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B25" s="2">
         <v>6105</v>
@@ -1468,10 +1709,20 @@
         <f t="shared" si="1"/>
         <v>1.2950040950040951</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I25" s="1">
+        <v>0</v>
+      </c>
+      <c r="J25" s="1">
+        <v>8124</v>
+      </c>
+      <c r="K25" s="7">
+        <f t="shared" si="2"/>
+        <v>1.3307125307125307</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B26" s="2">
         <v>6527</v>
@@ -1496,10 +1747,20 @@
         <f t="shared" si="1"/>
         <v>1.24712731729738</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I26" s="1">
+        <v>0</v>
+      </c>
+      <c r="J26" s="1">
+        <v>8215</v>
+      </c>
+      <c r="K26" s="7">
+        <f t="shared" si="2"/>
+        <v>1.2586180481078597</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B27" s="2">
         <v>533</v>
@@ -1524,10 +1785,20 @@
         <f t="shared" si="1"/>
         <v>1.1031894934333959</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I27" s="1">
+        <v>0</v>
+      </c>
+      <c r="J27" s="1">
+        <v>575</v>
+      </c>
+      <c r="K27" s="7">
+        <f t="shared" si="2"/>
+        <v>1.0787992495309568</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B28" s="2">
         <v>3854</v>
@@ -1552,10 +1823,20 @@
         <f t="shared" si="1"/>
         <v>1.3290088220031135</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I28" s="1">
+        <v>0</v>
+      </c>
+      <c r="J28" s="1">
+        <v>5481</v>
+      </c>
+      <c r="K28" s="7">
+        <f t="shared" si="2"/>
+        <v>1.4221587960560456</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B29" s="2">
         <v>2579</v>
@@ -1580,10 +1861,20 @@
         <f t="shared" si="1"/>
         <v>1.2846064366033347</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I29" s="1">
+        <v>0</v>
+      </c>
+      <c r="J29" s="1">
+        <v>3565</v>
+      </c>
+      <c r="K29" s="7">
+        <f t="shared" si="2"/>
+        <v>1.3823187281892206</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B30" s="2">
         <v>50778</v>
@@ -1608,10 +1899,20 @@
         <f t="shared" si="1"/>
         <v>1.3469809760132341</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I30" s="1">
+        <v>0</v>
+      </c>
+      <c r="J30" s="1">
+        <v>69347</v>
+      </c>
+      <c r="K30" s="7">
+        <f t="shared" si="2"/>
+        <v>1.3656898656898657</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B31" s="2">
         <v>259045</v>
@@ -1636,10 +1937,20 @@
         <f t="shared" si="1"/>
         <v>1.3404852438765464</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I31" s="1">
+        <v>3</v>
+      </c>
+      <c r="J31" s="1">
+        <v>345675</v>
+      </c>
+      <c r="K31" s="7">
+        <f t="shared" si="2"/>
+        <v>1.3344206605030013</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>5</v>
@@ -1656,11 +1967,17 @@
       </c>
       <c r="G32" s="5"/>
       <c r="H32" s="5"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I32" s="6">
+        <f>AVERAGE(I3:I31)</f>
+        <v>0.10344827586206896</v>
+      </c>
+      <c r="J32" s="5"/>
+      <c r="K32" s="5"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="5"/>
       <c r="B33" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C33" s="6">
         <f>AVERAGE(E4:E32)</f>
@@ -1674,12 +1991,21 @@
       </c>
       <c r="G33" s="5"/>
       <c r="H33" s="5"/>
+      <c r="I33" s="6">
+        <f>AVERAGE(K4:K32)</f>
+        <v>1.283560426015834</v>
+      </c>
+      <c r="J33" s="5"/>
+      <c r="K33" s="5"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:H31">
     <sortCondition ref="F3:F31"/>
   </sortState>
-  <mergeCells count="9">
+  <mergeCells count="12">
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="I32:K32"/>
+    <mergeCell ref="I33:K33"/>
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="F1:H1"/>

--- a/resource/result.xlsx
+++ b/resource/result.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b1fc4107772a6185/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="76" documentId="13_ncr:1_{8B51F813-F251-46DF-93E0-3CF12D1D0C85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB39C917-9143-4A67-8FA2-9A11F43B6787}"/>
+  <xr:revisionPtr revIDLastSave="77" documentId="13_ncr:1_{8B51F813-F251-46DF-93E0-3CF12D1D0C85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E19C7C9-BE20-4F65-9CE7-222EC2C3B929}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -288,7 +288,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -306,9 +306,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -873,13 +870,13 @@
         <f t="shared" ref="H3:H31" si="1">G3/B3</f>
         <v>1.1052631578947369</v>
       </c>
-      <c r="I3" s="1">
-        <v>0</v>
-      </c>
-      <c r="J3" s="1">
+      <c r="I3" s="2">
+        <v>0</v>
+      </c>
+      <c r="J3" s="2">
         <v>23</v>
       </c>
-      <c r="K3" s="7">
+      <c r="K3" s="3">
         <f>J3/B3</f>
         <v>1.2105263157894737</v>
       </c>
@@ -911,13 +908,13 @@
         <f t="shared" si="1"/>
         <v>1.0274914089347078</v>
       </c>
-      <c r="I4" s="1">
-        <v>0</v>
-      </c>
-      <c r="J4" s="1">
+      <c r="I4" s="2">
+        <v>0</v>
+      </c>
+      <c r="J4" s="2">
         <v>291</v>
       </c>
-      <c r="K4" s="7">
+      <c r="K4" s="3">
         <f t="shared" ref="K4:K31" si="2">J4/B4</f>
         <v>1</v>
       </c>
@@ -949,13 +946,13 @@
         <f t="shared" si="1"/>
         <v>1.0140845070422535</v>
       </c>
-      <c r="I5" s="1">
-        <v>0</v>
-      </c>
-      <c r="J5" s="1">
+      <c r="I5" s="2">
+        <v>0</v>
+      </c>
+      <c r="J5" s="2">
         <v>79</v>
       </c>
-      <c r="K5" s="7">
+      <c r="K5" s="3">
         <f t="shared" si="2"/>
         <v>1.1126760563380282</v>
       </c>
@@ -987,13 +984,13 @@
         <f t="shared" si="1"/>
         <v>1.0599520383693046</v>
       </c>
-      <c r="I6" s="1">
-        <v>0</v>
-      </c>
-      <c r="J6" s="1">
+      <c r="I6" s="2">
+        <v>0</v>
+      </c>
+      <c r="J6" s="2">
         <v>2352</v>
       </c>
-      <c r="K6" s="7">
+      <c r="K6" s="3">
         <f t="shared" si="2"/>
         <v>1.1280575539568345</v>
       </c>
@@ -1025,13 +1022,13 @@
         <f t="shared" si="1"/>
         <v>1.0273972602739727</v>
       </c>
-      <c r="I7" s="1">
-        <v>0</v>
-      </c>
-      <c r="J7" s="1">
+      <c r="I7" s="2">
+        <v>0</v>
+      </c>
+      <c r="J7" s="2">
         <v>83</v>
       </c>
-      <c r="K7" s="7">
+      <c r="K7" s="3">
         <f t="shared" si="2"/>
         <v>1.1369863013698631</v>
       </c>
@@ -1063,13 +1060,13 @@
         <f t="shared" si="1"/>
         <v>1.176093916755603</v>
       </c>
-      <c r="I8" s="1">
-        <v>0</v>
-      </c>
-      <c r="J8" s="1">
+      <c r="I8" s="2">
+        <v>0</v>
+      </c>
+      <c r="J8" s="2">
         <v>1112</v>
       </c>
-      <c r="K8" s="7">
+      <c r="K8" s="3">
         <f t="shared" si="2"/>
         <v>1.1867662753468518</v>
       </c>
@@ -1101,13 +1098,13 @@
         <f t="shared" si="1"/>
         <v>1.1397553179764135</v>
       </c>
-      <c r="I9" s="1">
-        <v>0</v>
-      </c>
-      <c r="J9" s="1">
+      <c r="I9" s="2">
+        <v>0</v>
+      </c>
+      <c r="J9" s="2">
         <v>11812</v>
       </c>
-      <c r="K9" s="7">
+      <c r="K9" s="3">
         <f t="shared" si="2"/>
         <v>1.3018847128843822</v>
       </c>
@@ -1139,13 +1136,13 @@
         <f t="shared" si="1"/>
         <v>1.1131324004305705</v>
       </c>
-      <c r="I10" s="1">
-        <v>0</v>
-      </c>
-      <c r="J10" s="1">
+      <c r="I10" s="2">
+        <v>0</v>
+      </c>
+      <c r="J10" s="2">
         <v>11812</v>
       </c>
-      <c r="K10" s="7">
+      <c r="K10" s="3">
         <f t="shared" si="2"/>
         <v>1.2714747039827772</v>
       </c>
@@ -1177,13 +1174,13 @@
         <f t="shared" si="1"/>
         <v>1.2287086477940519</v>
       </c>
-      <c r="I11" s="1">
-        <v>0</v>
-      </c>
-      <c r="J11" s="1">
+      <c r="I11" s="2">
+        <v>0</v>
+      </c>
+      <c r="J11" s="2">
         <v>43974</v>
       </c>
-      <c r="K11" s="7">
+      <c r="K11" s="3">
         <f t="shared" si="2"/>
         <v>1.31175610774692</v>
       </c>
@@ -1215,13 +1212,13 @@
         <f t="shared" si="1"/>
         <v>1.3051643192488263</v>
       </c>
-      <c r="I12" s="1">
-        <v>0</v>
-      </c>
-      <c r="J12" s="1">
+      <c r="I12" s="2">
+        <v>0</v>
+      </c>
+      <c r="J12" s="2">
         <v>581</v>
       </c>
-      <c r="K12" s="7">
+      <c r="K12" s="3">
         <f t="shared" si="2"/>
         <v>1.363849765258216</v>
       </c>
@@ -1253,13 +1250,13 @@
         <f t="shared" si="1"/>
         <v>1.2662423760275789</v>
       </c>
-      <c r="I13" s="1">
-        <v>0</v>
-      </c>
-      <c r="J13" s="1">
+      <c r="I13" s="2">
+        <v>0</v>
+      </c>
+      <c r="J13" s="2">
         <v>10114</v>
       </c>
-      <c r="K13" s="7">
+      <c r="K13" s="3">
         <f t="shared" si="2"/>
         <v>1.3410236011667993</v>
       </c>
@@ -1291,13 +1288,13 @@
         <f t="shared" si="1"/>
         <v>1.277037037037037</v>
       </c>
-      <c r="I14" s="1">
-        <v>0</v>
-      </c>
-      <c r="J14" s="1">
+      <c r="I14" s="2">
+        <v>0</v>
+      </c>
+      <c r="J14" s="2">
         <v>888</v>
       </c>
-      <c r="K14" s="7">
+      <c r="K14" s="3">
         <f t="shared" si="2"/>
         <v>1.3155555555555556</v>
       </c>
@@ -1329,13 +1326,13 @@
         <f t="shared" si="1"/>
         <v>1.2527881040892193</v>
       </c>
-      <c r="I15" s="1">
-        <v>0</v>
-      </c>
-      <c r="J15" s="1">
+      <c r="I15" s="2">
+        <v>0</v>
+      </c>
+      <c r="J15" s="2">
         <v>711</v>
       </c>
-      <c r="K15" s="7">
+      <c r="K15" s="3">
         <f t="shared" si="2"/>
         <v>1.3215613382899629</v>
       </c>
@@ -1367,13 +1364,13 @@
         <f t="shared" si="1"/>
         <v>1.3136678408639133</v>
       </c>
-      <c r="I16" s="1">
-        <v>0</v>
-      </c>
-      <c r="J16" s="1">
+      <c r="I16" s="2">
+        <v>0</v>
+      </c>
+      <c r="J16" s="2">
         <v>145336</v>
       </c>
-      <c r="K16" s="7">
+      <c r="K16" s="3">
         <f t="shared" si="2"/>
         <v>1.3437254412485322</v>
       </c>
@@ -1405,13 +1402,13 @@
         <f t="shared" si="1"/>
         <v>1.2629482071713147</v>
       </c>
-      <c r="I17" s="1">
-        <v>0</v>
-      </c>
-      <c r="J17" s="1">
+      <c r="I17" s="2">
+        <v>0</v>
+      </c>
+      <c r="J17" s="2">
         <v>666</v>
       </c>
-      <c r="K17" s="7">
+      <c r="K17" s="3">
         <f t="shared" si="2"/>
         <v>1.3266932270916334</v>
       </c>
@@ -1443,13 +1440,13 @@
         <f t="shared" si="1"/>
         <v>1.2424584155624472</v>
       </c>
-      <c r="I18" s="1">
-        <v>0</v>
-      </c>
-      <c r="J18" s="1">
+      <c r="I18" s="2">
+        <v>0</v>
+      </c>
+      <c r="J18" s="2">
         <v>27210</v>
       </c>
-      <c r="K18" s="7">
+      <c r="K18" s="3">
         <f t="shared" si="2"/>
         <v>1.2785452495066254</v>
       </c>
@@ -1481,13 +1478,13 @@
         <f t="shared" si="1"/>
         <v>1.3075328931514771</v>
       </c>
-      <c r="I19" s="1">
-        <v>0</v>
-      </c>
-      <c r="J19" s="1">
+      <c r="I19" s="2">
+        <v>0</v>
+      </c>
+      <c r="J19" s="2">
         <v>27968</v>
       </c>
-      <c r="K19" s="7">
+      <c r="K19" s="3">
         <f t="shared" si="2"/>
         <v>1.3479203817051424</v>
       </c>
@@ -1519,13 +1516,13 @@
         <f t="shared" si="1"/>
         <v>1.2210951441720672</v>
       </c>
-      <c r="I20" s="1">
-        <v>0</v>
-      </c>
-      <c r="J20" s="1">
+      <c r="I20" s="2">
+        <v>0</v>
+      </c>
+      <c r="J20" s="2">
         <v>27112</v>
       </c>
-      <c r="K20" s="7">
+      <c r="K20" s="3">
         <f t="shared" si="2"/>
         <v>1.2732225039917349</v>
       </c>
@@ -1557,13 +1554,13 @@
         <f t="shared" si="1"/>
         <v>1.3727917472598323</v>
       </c>
-      <c r="I21" s="1">
-        <v>0</v>
-      </c>
-      <c r="J21" s="1">
+      <c r="I21" s="2">
+        <v>0</v>
+      </c>
+      <c r="J21" s="2">
         <v>10796</v>
       </c>
-      <c r="K21" s="7">
+      <c r="K21" s="3">
         <f t="shared" si="2"/>
         <v>1.392134107027724</v>
       </c>
@@ -1595,13 +1592,13 @@
         <f t="shared" si="1"/>
         <v>1.3068362480127187</v>
       </c>
-      <c r="I22" s="1">
-        <v>0</v>
-      </c>
-      <c r="J22" s="1">
+      <c r="I22" s="2">
+        <v>0</v>
+      </c>
+      <c r="J22" s="2">
         <v>855</v>
       </c>
-      <c r="K22" s="7">
+      <c r="K22" s="3">
         <f t="shared" si="2"/>
         <v>1.3593004769475359</v>
       </c>
@@ -1633,13 +1630,13 @@
         <f t="shared" si="1"/>
         <v>1.3144864037832951</v>
       </c>
-      <c r="I23" s="1">
-        <v>0</v>
-      </c>
-      <c r="J23" s="1">
+      <c r="I23" s="2">
+        <v>0</v>
+      </c>
+      <c r="J23" s="2">
         <v>19623</v>
       </c>
-      <c r="K23" s="7">
+      <c r="K23" s="3">
         <f t="shared" si="2"/>
         <v>1.3646985186730649</v>
       </c>
@@ -1671,13 +1668,13 @@
         <f t="shared" si="1"/>
         <v>1.2603479304139171</v>
       </c>
-      <c r="I24" s="1">
-        <v>0</v>
-      </c>
-      <c r="J24" s="1">
+      <c r="I24" s="2">
+        <v>0</v>
+      </c>
+      <c r="J24" s="2">
         <v>2149</v>
       </c>
-      <c r="K24" s="7">
+      <c r="K24" s="3">
         <f t="shared" si="2"/>
         <v>1.2891421715656868</v>
       </c>
@@ -1709,13 +1706,13 @@
         <f t="shared" si="1"/>
         <v>1.2950040950040951</v>
       </c>
-      <c r="I25" s="1">
-        <v>0</v>
-      </c>
-      <c r="J25" s="1">
+      <c r="I25" s="2">
+        <v>0</v>
+      </c>
+      <c r="J25" s="2">
         <v>8124</v>
       </c>
-      <c r="K25" s="7">
+      <c r="K25" s="3">
         <f t="shared" si="2"/>
         <v>1.3307125307125307</v>
       </c>
@@ -1747,13 +1744,13 @@
         <f t="shared" si="1"/>
         <v>1.24712731729738</v>
       </c>
-      <c r="I26" s="1">
-        <v>0</v>
-      </c>
-      <c r="J26" s="1">
+      <c r="I26" s="2">
+        <v>0</v>
+      </c>
+      <c r="J26" s="2">
         <v>8215</v>
       </c>
-      <c r="K26" s="7">
+      <c r="K26" s="3">
         <f t="shared" si="2"/>
         <v>1.2586180481078597</v>
       </c>
@@ -1785,13 +1782,13 @@
         <f t="shared" si="1"/>
         <v>1.1031894934333959</v>
       </c>
-      <c r="I27" s="1">
-        <v>0</v>
-      </c>
-      <c r="J27" s="1">
+      <c r="I27" s="2">
+        <v>0</v>
+      </c>
+      <c r="J27" s="2">
         <v>575</v>
       </c>
-      <c r="K27" s="7">
+      <c r="K27" s="3">
         <f t="shared" si="2"/>
         <v>1.0787992495309568</v>
       </c>
@@ -1823,13 +1820,13 @@
         <f t="shared" si="1"/>
         <v>1.3290088220031135</v>
       </c>
-      <c r="I28" s="1">
-        <v>0</v>
-      </c>
-      <c r="J28" s="1">
+      <c r="I28" s="2">
+        <v>0</v>
+      </c>
+      <c r="J28" s="2">
         <v>5481</v>
       </c>
-      <c r="K28" s="7">
+      <c r="K28" s="3">
         <f t="shared" si="2"/>
         <v>1.4221587960560456</v>
       </c>
@@ -1861,13 +1858,13 @@
         <f t="shared" si="1"/>
         <v>1.2846064366033347</v>
       </c>
-      <c r="I29" s="1">
-        <v>0</v>
-      </c>
-      <c r="J29" s="1">
+      <c r="I29" s="2">
+        <v>0</v>
+      </c>
+      <c r="J29" s="2">
         <v>3565</v>
       </c>
-      <c r="K29" s="7">
+      <c r="K29" s="3">
         <f t="shared" si="2"/>
         <v>1.3823187281892206</v>
       </c>
@@ -1899,13 +1896,13 @@
         <f t="shared" si="1"/>
         <v>1.3469809760132341</v>
       </c>
-      <c r="I30" s="1">
-        <v>0</v>
-      </c>
-      <c r="J30" s="1">
+      <c r="I30" s="2">
+        <v>0</v>
+      </c>
+      <c r="J30" s="2">
         <v>69347</v>
       </c>
-      <c r="K30" s="7">
+      <c r="K30" s="3">
         <f t="shared" si="2"/>
         <v>1.3656898656898657</v>
       </c>
@@ -1937,13 +1934,13 @@
         <f t="shared" si="1"/>
         <v>1.3404852438765464</v>
       </c>
-      <c r="I31" s="1">
+      <c r="I31" s="2">
         <v>3</v>
       </c>
-      <c r="J31" s="1">
+      <c r="J31" s="2">
         <v>345675</v>
       </c>
-      <c r="K31" s="7">
+      <c r="K31" s="3">
         <f t="shared" si="2"/>
         <v>1.3344206605030013</v>
       </c>
@@ -2003,18 +2000,18 @@
     <sortCondition ref="F3:F31"/>
   </sortState>
   <mergeCells count="12">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="F33:H33"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="I32:K32"/>
     <mergeCell ref="I33:K33"/>
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="C32:E32"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="C33:E33"/>
-    <mergeCell ref="F33:H33"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/resource/result.xlsx
+++ b/resource/result.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b1fc4107772a6185/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_Files\_Lessons\ALGORITHM\Project\resource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="77" documentId="13_ncr:1_{8B51F813-F251-46DF-93E0-3CF12D1D0C85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E19C7C9-BE20-4F65-9CE7-222EC2C3B929}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{211E5A1A-E151-4AC4-8963-F44BD1DDFC75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXACT" sheetId="9" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="49">
   <si>
     <t>att48</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -781,7 +781,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{260DB66E-1FFD-4D32-BA5D-DB6972467A37}">
-  <dimension ref="A1:K33"/>
+  <dimension ref="A1:X33"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.33203125" style="1" customWidth="1"/>
@@ -789,7 +789,7 @@
     <col min="3" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>44</v>
       </c>
@@ -811,8 +811,29 @@
       </c>
       <c r="J1" s="5"/>
       <c r="K1" s="5"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="N1" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="P1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q1" s="5"/>
+      <c r="R1" s="5"/>
+      <c r="S1" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="T1" s="5"/>
+      <c r="U1" s="5"/>
+      <c r="V1" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="W1" s="5"/>
+      <c r="X1" s="5"/>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A2" s="5"/>
       <c r="B2" s="5"/>
       <c r="C2" s="2" t="s">
@@ -842,8 +863,37 @@
       <c r="K2" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>19</v>
       </c>
@@ -880,8 +930,44 @@
         <f>J3/B3</f>
         <v>1.2105263157894737</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="N3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O3" s="2">
+        <v>19</v>
+      </c>
+      <c r="P3" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>21</v>
+      </c>
+      <c r="R3" s="3">
+        <f t="shared" ref="R3:R4" si="2">Q3/O3</f>
+        <v>1.1052631578947369</v>
+      </c>
+      <c r="S3" s="2">
+        <v>0</v>
+      </c>
+      <c r="T3" s="2">
+        <v>21</v>
+      </c>
+      <c r="U3" s="3">
+        <f t="shared" ref="U3:U4" si="3">T3/O3</f>
+        <v>1.1052631578947369</v>
+      </c>
+      <c r="V3" s="2">
+        <v>0</v>
+      </c>
+      <c r="W3" s="2">
+        <v>23</v>
+      </c>
+      <c r="X3" s="3">
+        <f>W3/O3</f>
+        <v>1.2105263157894737</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
@@ -915,11 +1001,47 @@
         <v>291</v>
       </c>
       <c r="K4" s="3">
-        <f t="shared" ref="K4:K31" si="2">J4/B4</f>
+        <f t="shared" ref="K4:K31" si="4">J4/B4</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="N4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="O4" s="2">
+        <v>291</v>
+      </c>
+      <c r="P4" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>291</v>
+      </c>
+      <c r="R4" s="3">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="S4" s="2">
+        <v>0</v>
+      </c>
+      <c r="T4" s="2">
+        <v>299</v>
+      </c>
+      <c r="U4" s="3">
+        <f t="shared" si="3"/>
+        <v>1.0274914089347078</v>
+      </c>
+      <c r="V4" s="2">
+        <v>0</v>
+      </c>
+      <c r="W4" s="2">
+        <v>291</v>
+      </c>
+      <c r="X4" s="3">
+        <f t="shared" ref="X4" si="5">W4/O4</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>35</v>
       </c>
@@ -953,11 +1075,47 @@
         <v>79</v>
       </c>
       <c r="K5" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.1126760563380282</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="N5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O5" s="2">
+        <v>937</v>
+      </c>
+      <c r="P5" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>965</v>
+      </c>
+      <c r="R5" s="3">
+        <f>Q5/O5</f>
+        <v>1.0298826040554963</v>
+      </c>
+      <c r="S5" s="2">
+        <v>0</v>
+      </c>
+      <c r="T5" s="2">
+        <v>1102</v>
+      </c>
+      <c r="U5" s="3">
+        <f>T5/O5</f>
+        <v>1.176093916755603</v>
+      </c>
+      <c r="V5" s="2">
+        <v>0</v>
+      </c>
+      <c r="W5" s="2">
+        <v>1112</v>
+      </c>
+      <c r="X5" s="3">
+        <f>W5/O5</f>
+        <v>1.1867662753468518</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>22</v>
       </c>
@@ -991,11 +1149,47 @@
         <v>2352</v>
       </c>
       <c r="K6" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.1280575539568345</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="N6" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="O6" s="2">
+        <v>33523</v>
+      </c>
+      <c r="P6" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>37928</v>
+      </c>
+      <c r="R6" s="3">
+        <f>Q6/O6</f>
+        <v>1.1314023207946782</v>
+      </c>
+      <c r="S6" s="2">
+        <v>6</v>
+      </c>
+      <c r="T6" s="2">
+        <v>41190</v>
+      </c>
+      <c r="U6" s="3">
+        <f>T6/O6</f>
+        <v>1.2287086477940519</v>
+      </c>
+      <c r="V6" s="2">
+        <v>0</v>
+      </c>
+      <c r="W6" s="2">
+        <v>43974</v>
+      </c>
+      <c r="X6" s="3">
+        <f>W6/O6</f>
+        <v>1.31175610774692</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>36</v>
       </c>
@@ -1029,11 +1223,47 @@
         <v>83</v>
       </c>
       <c r="K7" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.1369863013698631</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="N7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O7" s="2">
+        <v>675</v>
+      </c>
+      <c r="P7" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>796</v>
+      </c>
+      <c r="R7" s="3">
+        <f>Q7/O7</f>
+        <v>1.1792592592592592</v>
+      </c>
+      <c r="S7" s="2">
+        <v>22</v>
+      </c>
+      <c r="T7" s="2">
+        <v>862</v>
+      </c>
+      <c r="U7" s="3">
+        <f>T7/O7</f>
+        <v>1.277037037037037</v>
+      </c>
+      <c r="V7" s="2">
+        <v>0</v>
+      </c>
+      <c r="W7" s="2">
+        <v>888</v>
+      </c>
+      <c r="X7" s="3">
+        <f>W7/O7</f>
+        <v>1.3155555555555556</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>20</v>
       </c>
@@ -1067,11 +1297,47 @@
         <v>1112</v>
       </c>
       <c r="K8" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.1867662753468518</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="N8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="O8" s="2">
+        <v>502</v>
+      </c>
+      <c r="P8" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>583</v>
+      </c>
+      <c r="R8" s="3">
+        <f>Q8/O8</f>
+        <v>1.1613545816733069</v>
+      </c>
+      <c r="S8" s="2">
+        <v>69</v>
+      </c>
+      <c r="T8" s="2">
+        <v>634</v>
+      </c>
+      <c r="U8" s="3">
+        <f>T8/O8</f>
+        <v>1.2629482071713147</v>
+      </c>
+      <c r="V8" s="2">
+        <v>0</v>
+      </c>
+      <c r="W8" s="2">
+        <v>666</v>
+      </c>
+      <c r="X8" s="3">
+        <f>W8/O8</f>
+        <v>1.3266932270916334</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>11</v>
       </c>
@@ -1105,11 +1371,47 @@
         <v>11812</v>
       </c>
       <c r="K9" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3018847128843822</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="N9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O9" s="2">
+        <v>21294</v>
+      </c>
+      <c r="P9" s="2">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>24852</v>
+      </c>
+      <c r="R9" s="3">
+        <f>Q9/O9</f>
+        <v>1.1670893209354747</v>
+      </c>
+      <c r="S9" s="2">
+        <v>84</v>
+      </c>
+      <c r="T9" s="2">
+        <v>26002</v>
+      </c>
+      <c r="U9" s="3">
+        <f>T9/O9</f>
+        <v>1.2210951441720672</v>
+      </c>
+      <c r="V9" s="2">
+        <v>0</v>
+      </c>
+      <c r="W9" s="2">
+        <v>27112</v>
+      </c>
+      <c r="X9" s="3">
+        <f>W9/O9</f>
+        <v>1.2732225039917349</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>12</v>
       </c>
@@ -1143,11 +1445,47 @@
         <v>11812</v>
       </c>
       <c r="K10" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.2714747039827772</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="N10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="O10" s="2">
+        <v>1667</v>
+      </c>
+      <c r="P10" s="2">
+        <v>4</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>1836</v>
+      </c>
+      <c r="R10" s="3">
+        <f>Q10/O10</f>
+        <v>1.101379724055189</v>
+      </c>
+      <c r="S10" s="2">
+        <v>169</v>
+      </c>
+      <c r="T10" s="2">
+        <v>2101</v>
+      </c>
+      <c r="U10" s="3">
+        <f>T10/O10</f>
+        <v>1.2603479304139171</v>
+      </c>
+      <c r="V10" s="2">
+        <v>0</v>
+      </c>
+      <c r="W10" s="2">
+        <v>2149</v>
+      </c>
+      <c r="X10" s="3">
+        <f>W10/O10</f>
+        <v>1.2891421715656868</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>0</v>
       </c>
@@ -1181,11 +1519,47 @@
         <v>43974</v>
       </c>
       <c r="K11" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.31175610774692</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="N11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O11" s="2">
+        <v>6527</v>
+      </c>
+      <c r="P11" s="2">
+        <v>9</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>7213</v>
+      </c>
+      <c r="R11" s="3">
+        <f>Q11/O11</f>
+        <v>1.105101884479853</v>
+      </c>
+      <c r="S11" s="2">
+        <v>416</v>
+      </c>
+      <c r="T11" s="2">
+        <v>8140</v>
+      </c>
+      <c r="U11" s="3">
+        <f>T11/O11</f>
+        <v>1.24712731729738</v>
+      </c>
+      <c r="V11" s="2">
+        <v>0</v>
+      </c>
+      <c r="W11" s="2">
+        <v>8215</v>
+      </c>
+      <c r="X11" s="3">
+        <f>W11/O11</f>
+        <v>1.2586180481078597</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>17</v>
       </c>
@@ -1219,11 +1593,47 @@
         <v>581</v>
       </c>
       <c r="K12" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.363849765258216</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="N12" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="O12" s="2">
+        <v>533</v>
+      </c>
+      <c r="P12" s="2">
+        <v>13</v>
+      </c>
+      <c r="Q12" s="2">
+        <v>547</v>
+      </c>
+      <c r="R12" s="3">
+        <f>Q12/O12</f>
+        <v>1.026266416510319</v>
+      </c>
+      <c r="S12" s="2">
+        <v>1306</v>
+      </c>
+      <c r="T12" s="2">
+        <v>588</v>
+      </c>
+      <c r="U12" s="3">
+        <f>T12/O12</f>
+        <v>1.1031894934333959</v>
+      </c>
+      <c r="V12" s="2">
+        <v>0</v>
+      </c>
+      <c r="W12" s="2">
+        <v>575</v>
+      </c>
+      <c r="X12" s="3">
+        <f>W12/O12</f>
+        <v>1.0787992495309568</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>13</v>
       </c>
@@ -1257,11 +1667,47 @@
         <v>10114</v>
       </c>
       <c r="K13" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3410236011667993</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="N13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="O13" s="2">
+        <v>2579</v>
+      </c>
+      <c r="P13" s="2">
+        <v>31</v>
+      </c>
+      <c r="Q13" s="2">
+        <v>2975</v>
+      </c>
+      <c r="R13" s="3">
+        <f>Q13/O13</f>
+        <v>1.1535478867778208</v>
+      </c>
+      <c r="S13" s="2">
+        <v>4514</v>
+      </c>
+      <c r="T13" s="2">
+        <v>3313</v>
+      </c>
+      <c r="U13" s="3">
+        <f>T13/O13</f>
+        <v>1.2846064366033347</v>
+      </c>
+      <c r="V13" s="2">
+        <v>0</v>
+      </c>
+      <c r="W13" s="2">
+        <v>3565</v>
+      </c>
+      <c r="X13" s="3">
+        <f>W13/O13</f>
+        <v>1.3823187281892206</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>33</v>
       </c>
@@ -1295,11 +1741,47 @@
         <v>888</v>
       </c>
       <c r="K14" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3155555555555556</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="N14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O14" s="2">
+        <v>50778</v>
+      </c>
+      <c r="P14" s="2">
+        <v>132</v>
+      </c>
+      <c r="Q14" s="2">
+        <v>58950</v>
+      </c>
+      <c r="R14" s="3">
+        <f>Q14/O14</f>
+        <v>1.1609358383551931</v>
+      </c>
+      <c r="S14" s="2">
+        <v>29490</v>
+      </c>
+      <c r="T14" s="2">
+        <v>68397</v>
+      </c>
+      <c r="U14" s="3">
+        <f>T14/O14</f>
+        <v>1.3469809760132341</v>
+      </c>
+      <c r="V14" s="2">
+        <v>0</v>
+      </c>
+      <c r="W14" s="2">
+        <v>69347</v>
+      </c>
+      <c r="X14" s="3">
+        <f>W14/O14</f>
+        <v>1.3656898656898657</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>18</v>
       </c>
@@ -1333,11 +1815,47 @@
         <v>711</v>
       </c>
       <c r="K15" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3215613382899629</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="N15" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="O15" s="2">
+        <v>259045</v>
+      </c>
+      <c r="P15" s="2">
+        <v>1196</v>
+      </c>
+      <c r="Q15" s="2">
+        <v>313745</v>
+      </c>
+      <c r="R15" s="3">
+        <f>Q15/O15</f>
+        <v>1.2111602231272558</v>
+      </c>
+      <c r="S15" s="2">
+        <v>502354</v>
+      </c>
+      <c r="T15" s="2">
+        <v>347246</v>
+      </c>
+      <c r="U15" s="3">
+        <f>T15/O15</f>
+        <v>1.3404852438765464</v>
+      </c>
+      <c r="V15" s="2">
+        <v>3</v>
+      </c>
+      <c r="W15" s="2">
+        <v>345675</v>
+      </c>
+      <c r="X15" s="3">
+        <f>W15/O15</f>
+        <v>1.3344206605030013</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>31</v>
       </c>
@@ -1371,11 +1889,35 @@
         <v>145336</v>
       </c>
       <c r="K16" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3437254412485322</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="N16" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="P16" s="6">
+        <f>AVERAGE(P3:P15)</f>
+        <v>107</v>
+      </c>
+      <c r="Q16" s="5"/>
+      <c r="R16" s="5"/>
+      <c r="S16" s="6">
+        <f>AVERAGE(S3:S15)</f>
+        <v>41417.692307692305</v>
+      </c>
+      <c r="T16" s="5"/>
+      <c r="U16" s="5"/>
+      <c r="V16" s="6">
+        <f>AVERAGE(V3:V15)</f>
+        <v>0.23076923076923078</v>
+      </c>
+      <c r="W16" s="5"/>
+      <c r="X16" s="5"/>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>24</v>
       </c>
@@ -1409,11 +1951,33 @@
         <v>666</v>
       </c>
       <c r="K17" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3266932270916334</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="N17" s="5"/>
+      <c r="O17" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="P17" s="6">
+        <f>AVERAGE(R4:R16)</f>
+        <v>1.1189483383353205</v>
+      </c>
+      <c r="Q17" s="5"/>
+      <c r="R17" s="5"/>
+      <c r="S17" s="6">
+        <f>AVERAGE(U4:U16)</f>
+        <v>1.231342646625216</v>
+      </c>
+      <c r="T17" s="5"/>
+      <c r="U17" s="5"/>
+      <c r="V17" s="6">
+        <f>AVERAGE(X4:X16)</f>
+        <v>1.2602485327766073</v>
+      </c>
+      <c r="W17" s="5"/>
+      <c r="X17" s="5"/>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>25</v>
       </c>
@@ -1447,11 +2011,11 @@
         <v>27210</v>
       </c>
       <c r="K18" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.2785452495066254</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>26</v>
       </c>
@@ -1485,11 +2049,11 @@
         <v>27968</v>
       </c>
       <c r="K19" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3479203817051424</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>27</v>
       </c>
@@ -1523,11 +2087,11 @@
         <v>27112</v>
       </c>
       <c r="K20" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.2732225039917349</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>32</v>
       </c>
@@ -1561,11 +2125,11 @@
         <v>10796</v>
       </c>
       <c r="K21" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.392134107027724</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>16</v>
       </c>
@@ -1599,11 +2163,11 @@
         <v>855</v>
       </c>
       <c r="K22" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3593004769475359</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>28</v>
       </c>
@@ -1637,11 +2201,11 @@
         <v>19623</v>
       </c>
       <c r="K23" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3646985186730649</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>21</v>
       </c>
@@ -1675,11 +2239,11 @@
         <v>2149</v>
       </c>
       <c r="K24" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.2891421715656868</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>14</v>
       </c>
@@ -1713,11 +2277,11 @@
         <v>8124</v>
       </c>
       <c r="K25" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3307125307125307</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>15</v>
       </c>
@@ -1751,11 +2315,11 @@
         <v>8215</v>
       </c>
       <c r="K26" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.2586180481078597</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>23</v>
       </c>
@@ -1789,11 +2353,11 @@
         <v>575</v>
       </c>
       <c r="K27" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.0787992495309568</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>34</v>
       </c>
@@ -1827,11 +2391,11 @@
         <v>5481</v>
       </c>
       <c r="K28" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.4221587960560456</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>10</v>
       </c>
@@ -1865,11 +2429,11 @@
         <v>3565</v>
       </c>
       <c r="K29" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3823187281892206</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>29</v>
       </c>
@@ -1903,11 +2467,11 @@
         <v>69347</v>
       </c>
       <c r="K30" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3656898656898657</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>30</v>
       </c>
@@ -1941,11 +2505,11 @@
         <v>345675</v>
       </c>
       <c r="K31" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3344206605030013</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
         <v>45</v>
       </c>
@@ -1999,19 +2563,31 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:H31">
     <sortCondition ref="F3:F31"/>
   </sortState>
-  <mergeCells count="12">
+  <mergeCells count="24">
+    <mergeCell ref="N16:N17"/>
+    <mergeCell ref="P16:R16"/>
+    <mergeCell ref="S16:U16"/>
+    <mergeCell ref="V16:X16"/>
+    <mergeCell ref="P17:R17"/>
+    <mergeCell ref="S17:U17"/>
+    <mergeCell ref="V17:X17"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:R1"/>
+    <mergeCell ref="S1:U1"/>
+    <mergeCell ref="V1:X1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="I32:K32"/>
+    <mergeCell ref="I33:K33"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="F1:H1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="C32:E32"/>
     <mergeCell ref="F32:H32"/>
     <mergeCell ref="A32:A33"/>
     <mergeCell ref="C33:E33"/>
     <mergeCell ref="F33:H33"/>
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="I32:K32"/>
-    <mergeCell ref="I33:K33"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="F1:H1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/resource/result.xlsx
+++ b/resource/result.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_Files\_Lessons\ALGORITHM\Project\resource\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{211E5A1A-E151-4AC4-8963-F44BD1DDFC75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DD0BCDD-4C87-4B82-B61B-58E0B8F848A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXACT" sheetId="9" r:id="rId1"/>
@@ -917,7 +917,7 @@
         <v>21</v>
       </c>
       <c r="H3" s="3">
-        <f t="shared" ref="H3:H31" si="1">G3/B3</f>
+        <f>G3/B3</f>
         <v>1.1052631578947369</v>
       </c>
       <c r="I3" s="2">
@@ -943,7 +943,7 @@
         <v>21</v>
       </c>
       <c r="R3" s="3">
-        <f t="shared" ref="R3:R4" si="2">Q3/O3</f>
+        <f t="shared" ref="R3:R4" si="1">Q3/O3</f>
         <v>1.1052631578947369</v>
       </c>
       <c r="S3" s="2">
@@ -953,7 +953,7 @@
         <v>21</v>
       </c>
       <c r="U3" s="3">
-        <f t="shared" ref="U3:U4" si="3">T3/O3</f>
+        <f t="shared" ref="U3:U4" si="2">T3/O3</f>
         <v>1.1052631578947369</v>
       </c>
       <c r="V3" s="2">
@@ -991,18 +991,18 @@
         <v>299</v>
       </c>
       <c r="H4" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="H4:H31" si="3">G4/B4</f>
         <v>1.0274914089347078</v>
       </c>
       <c r="I4" s="2">
         <v>0</v>
       </c>
       <c r="J4" s="2">
-        <v>291</v>
+        <v>366</v>
       </c>
       <c r="K4" s="3">
         <f t="shared" ref="K4:K31" si="4">J4/B4</f>
-        <v>1</v>
+        <v>1.2577319587628866</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>1</v>
@@ -1017,7 +1017,7 @@
         <v>291</v>
       </c>
       <c r="R4" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S4" s="2">
@@ -1027,18 +1027,18 @@
         <v>299</v>
       </c>
       <c r="U4" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1.0274914089347078</v>
       </c>
       <c r="V4" s="2">
         <v>0</v>
       </c>
       <c r="W4" s="2">
-        <v>291</v>
+        <v>366</v>
       </c>
       <c r="X4" s="3">
         <f t="shared" ref="X4" si="5">W4/O4</f>
-        <v>1</v>
+        <v>1.2577319587628866</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.3">
@@ -1065,7 +1065,7 @@
         <v>72</v>
       </c>
       <c r="H5" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.0140845070422535</v>
       </c>
       <c r="I5" s="2">
@@ -1091,17 +1091,17 @@
         <v>965</v>
       </c>
       <c r="R5" s="3">
-        <f>Q5/O5</f>
+        <f t="shared" ref="R5:R15" si="6">Q5/O5</f>
         <v>1.0298826040554963</v>
       </c>
       <c r="S5" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T5" s="2">
         <v>1102</v>
       </c>
       <c r="U5" s="3">
-        <f>T5/O5</f>
+        <f t="shared" ref="U5:U15" si="7">T5/O5</f>
         <v>1.176093916755603</v>
       </c>
       <c r="V5" s="2">
@@ -1111,7 +1111,7 @@
         <v>1112</v>
       </c>
       <c r="X5" s="3">
-        <f>W5/O5</f>
+        <f t="shared" ref="X5:X15" si="8">W5/O5</f>
         <v>1.1867662753468518</v>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
         <v>1.0446043165467627</v>
       </c>
       <c r="F6" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="2">
         <v>2210</v>
       </c>
       <c r="H6" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.0599520383693046</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" s="2">
         <v>2352</v>
@@ -1165,17 +1165,17 @@
         <v>37928</v>
       </c>
       <c r="R6" s="3">
-        <f>Q6/O6</f>
+        <f t="shared" si="6"/>
         <v>1.1314023207946782</v>
       </c>
       <c r="S6" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T6" s="2">
         <v>41190</v>
       </c>
       <c r="U6" s="3">
-        <f>T6/O6</f>
+        <f t="shared" si="7"/>
         <v>1.2287086477940519</v>
       </c>
       <c r="V6" s="2">
@@ -1185,7 +1185,7 @@
         <v>43974</v>
       </c>
       <c r="X6" s="3">
-        <f>W6/O6</f>
+        <f t="shared" si="8"/>
         <v>1.31175610774692</v>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
         <v>1.178082191780822</v>
       </c>
       <c r="F7" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7" s="2">
         <v>75</v>
       </c>
       <c r="H7" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.0273972602739727</v>
       </c>
       <c r="I7" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" s="2">
         <v>83</v>
@@ -1239,28 +1239,28 @@
         <v>796</v>
       </c>
       <c r="R7" s="3">
-        <f>Q7/O7</f>
+        <f t="shared" si="6"/>
         <v>1.1792592592592592</v>
       </c>
       <c r="S7" s="2">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="T7" s="2">
         <v>862</v>
       </c>
       <c r="U7" s="3">
-        <f>T7/O7</f>
+        <f t="shared" si="7"/>
         <v>1.277037037037037</v>
       </c>
       <c r="V7" s="2">
         <v>0</v>
       </c>
       <c r="W7" s="2">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="X7" s="3">
-        <f>W7/O7</f>
-        <v>1.3155555555555556</v>
+        <f t="shared" si="8"/>
+        <v>1.3214814814814815</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.3">
@@ -1281,13 +1281,13 @@
         <v>1.0298826040554963</v>
       </c>
       <c r="F8" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" s="2">
         <v>1102</v>
       </c>
       <c r="H8" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.176093916755603</v>
       </c>
       <c r="I8" s="2">
@@ -1313,28 +1313,28 @@
         <v>583</v>
       </c>
       <c r="R8" s="3">
-        <f>Q8/O8</f>
+        <f t="shared" si="6"/>
         <v>1.1613545816733069</v>
       </c>
       <c r="S8" s="2">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="T8" s="2">
         <v>634</v>
       </c>
       <c r="U8" s="3">
-        <f>T8/O8</f>
+        <f t="shared" si="7"/>
         <v>1.2629482071713147</v>
       </c>
       <c r="V8" s="2">
         <v>0</v>
       </c>
       <c r="W8" s="2">
-        <v>666</v>
+        <v>648</v>
       </c>
       <c r="X8" s="3">
-        <f>W8/O8</f>
-        <v>1.3266932270916334</v>
+        <f t="shared" si="8"/>
+        <v>1.2908366533864541</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.3">
@@ -1361,7 +1361,7 @@
         <v>10341</v>
       </c>
       <c r="H9" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.1397553179764135</v>
       </c>
       <c r="I9" s="2">
@@ -1387,27 +1387,27 @@
         <v>24852</v>
       </c>
       <c r="R9" s="3">
-        <f>Q9/O9</f>
+        <f t="shared" si="6"/>
         <v>1.1670893209354747</v>
       </c>
       <c r="S9" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T9" s="2">
         <v>26002</v>
       </c>
       <c r="U9" s="3">
-        <f>T9/O9</f>
+        <f t="shared" si="7"/>
         <v>1.2210951441720672</v>
       </c>
       <c r="V9" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W9" s="2">
         <v>27112</v>
       </c>
       <c r="X9" s="3">
-        <f>W9/O9</f>
+        <f t="shared" si="8"/>
         <v>1.2732225039917349</v>
       </c>
     </row>
@@ -1429,13 +1429,13 @@
         <v>1.0723358449946179</v>
       </c>
       <c r="F10" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G10" s="2">
         <v>10341</v>
       </c>
       <c r="H10" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.1131324004305705</v>
       </c>
       <c r="I10" s="2">
@@ -1461,28 +1461,28 @@
         <v>1836</v>
       </c>
       <c r="R10" s="3">
-        <f>Q10/O10</f>
+        <f t="shared" si="6"/>
         <v>1.101379724055189</v>
       </c>
       <c r="S10" s="2">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="T10" s="2">
         <v>2101</v>
       </c>
       <c r="U10" s="3">
-        <f>T10/O10</f>
+        <f t="shared" si="7"/>
         <v>1.2603479304139171</v>
       </c>
       <c r="V10" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W10" s="2">
-        <v>2149</v>
+        <v>2160</v>
       </c>
       <c r="X10" s="3">
-        <f>W10/O10</f>
-        <v>1.2891421715656868</v>
+        <f t="shared" si="8"/>
+        <v>1.2957408518296341</v>
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.3">
@@ -1503,13 +1503,13 @@
         <v>1.1314023207946782</v>
       </c>
       <c r="F11" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G11" s="2">
         <v>41190</v>
       </c>
       <c r="H11" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.2287086477940519</v>
       </c>
       <c r="I11" s="2">
@@ -1535,28 +1535,28 @@
         <v>7213</v>
       </c>
       <c r="R11" s="3">
-        <f>Q11/O11</f>
+        <f t="shared" si="6"/>
         <v>1.105101884479853</v>
       </c>
       <c r="S11" s="2">
-        <v>416</v>
+        <v>437</v>
       </c>
       <c r="T11" s="2">
         <v>8140</v>
       </c>
       <c r="U11" s="3">
-        <f>T11/O11</f>
+        <f t="shared" si="7"/>
         <v>1.24712731729738</v>
       </c>
       <c r="V11" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W11" s="2">
-        <v>8215</v>
+        <v>8148</v>
       </c>
       <c r="X11" s="3">
-        <f>W11/O11</f>
-        <v>1.2586180481078597</v>
+        <f t="shared" si="8"/>
+        <v>1.2483529952504979</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.3">
@@ -1577,24 +1577,24 @@
         <v>1.1314553990610328</v>
       </c>
       <c r="F12" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G12" s="2">
         <v>556</v>
       </c>
       <c r="H12" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.3051643192488263</v>
       </c>
       <c r="I12" s="2">
         <v>0</v>
       </c>
       <c r="J12" s="2">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="K12" s="3">
         <f t="shared" si="4"/>
-        <v>1.363849765258216</v>
+        <v>1.3708920187793427</v>
       </c>
       <c r="N12" s="2" t="s">
         <v>23</v>
@@ -1609,28 +1609,28 @@
         <v>547</v>
       </c>
       <c r="R12" s="3">
-        <f>Q12/O12</f>
+        <f t="shared" si="6"/>
         <v>1.026266416510319</v>
       </c>
       <c r="S12" s="2">
-        <v>1306</v>
+        <v>1413</v>
       </c>
       <c r="T12" s="2">
         <v>588</v>
       </c>
       <c r="U12" s="3">
-        <f>T12/O12</f>
+        <f t="shared" si="7"/>
         <v>1.1031894934333959</v>
       </c>
       <c r="V12" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W12" s="2">
-        <v>575</v>
+        <v>598</v>
       </c>
       <c r="X12" s="3">
-        <f>W12/O12</f>
-        <v>1.0787992495309568</v>
+        <f t="shared" si="8"/>
+        <v>1.1219512195121952</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.3">
@@ -1657,11 +1657,11 @@
         <v>9550</v>
       </c>
       <c r="H13" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.2662423760275789</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J13" s="2">
         <v>10114</v>
@@ -1683,28 +1683,28 @@
         <v>2975</v>
       </c>
       <c r="R13" s="3">
-        <f>Q13/O13</f>
+        <f t="shared" si="6"/>
         <v>1.1535478867778208</v>
       </c>
       <c r="S13" s="2">
-        <v>4514</v>
+        <v>4774</v>
       </c>
       <c r="T13" s="2">
         <v>3313</v>
       </c>
       <c r="U13" s="3">
-        <f>T13/O13</f>
+        <f t="shared" si="7"/>
         <v>1.2846064366033347</v>
       </c>
       <c r="V13" s="2">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W13" s="2">
-        <v>3565</v>
+        <v>3580</v>
       </c>
       <c r="X13" s="3">
-        <f>W13/O13</f>
-        <v>1.3823187281892206</v>
+        <f t="shared" si="8"/>
+        <v>1.3881349360217139</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.3">
@@ -1725,24 +1725,24 @@
         <v>1.1792592592592592</v>
       </c>
       <c r="F14" s="2">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G14" s="2">
         <v>862</v>
       </c>
       <c r="H14" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.277037037037037</v>
       </c>
       <c r="I14" s="2">
         <v>0</v>
       </c>
       <c r="J14" s="2">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="K14" s="3">
         <f t="shared" si="4"/>
-        <v>1.3155555555555556</v>
+        <v>1.3214814814814815</v>
       </c>
       <c r="N14" s="2" t="s">
         <v>29</v>
@@ -1757,28 +1757,28 @@
         <v>58950</v>
       </c>
       <c r="R14" s="3">
-        <f>Q14/O14</f>
+        <f t="shared" si="6"/>
         <v>1.1609358383551931</v>
       </c>
       <c r="S14" s="2">
-        <v>29490</v>
+        <v>39353</v>
       </c>
       <c r="T14" s="2">
         <v>68397</v>
       </c>
       <c r="U14" s="3">
-        <f>T14/O14</f>
+        <f t="shared" si="7"/>
         <v>1.3469809760132341</v>
       </c>
       <c r="V14" s="2">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="W14" s="2">
-        <v>69347</v>
+        <v>69223</v>
       </c>
       <c r="X14" s="3">
-        <f>W14/O14</f>
-        <v>1.3656898656898657</v>
+        <f t="shared" si="8"/>
+        <v>1.3632478632478633</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.3">
@@ -1799,24 +1799,24 @@
         <v>1.1301115241635689</v>
       </c>
       <c r="F15" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G15" s="2">
         <v>674</v>
       </c>
       <c r="H15" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.2527881040892193</v>
       </c>
       <c r="I15" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" s="2">
-        <v>711</v>
+        <v>696</v>
       </c>
       <c r="K15" s="3">
         <f t="shared" si="4"/>
-        <v>1.3215613382899629</v>
+        <v>1.2936802973977695</v>
       </c>
       <c r="N15" s="2" t="s">
         <v>30</v>
@@ -1831,28 +1831,28 @@
         <v>313745</v>
       </c>
       <c r="R15" s="3">
-        <f>Q15/O15</f>
+        <f t="shared" si="6"/>
         <v>1.2111602231272558</v>
       </c>
       <c r="S15" s="2">
-        <v>502354</v>
+        <v>696928</v>
       </c>
       <c r="T15" s="2">
         <v>347246</v>
       </c>
       <c r="U15" s="3">
-        <f>T15/O15</f>
+        <f t="shared" si="7"/>
         <v>1.3404852438765464</v>
       </c>
       <c r="V15" s="2">
-        <v>3</v>
+        <v>519</v>
       </c>
       <c r="W15" s="2">
-        <v>345675</v>
+        <v>348709</v>
       </c>
       <c r="X15" s="3">
-        <f>W15/O15</f>
-        <v>1.3344206605030013</v>
+        <f t="shared" si="8"/>
+        <v>1.3461329112702427</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.3">
@@ -1873,13 +1873,13 @@
         <v>1.2104494309303895</v>
       </c>
       <c r="F16" s="2">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G16" s="2">
         <v>142085</v>
       </c>
       <c r="H16" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.3136678408639133</v>
       </c>
       <c r="I16" s="2">
@@ -1906,13 +1906,13 @@
       <c r="R16" s="5"/>
       <c r="S16" s="6">
         <f>AVERAGE(S3:S15)</f>
-        <v>41417.692307692305</v>
+        <v>57174.923076923078</v>
       </c>
       <c r="T16" s="5"/>
       <c r="U16" s="5"/>
       <c r="V16" s="6">
         <f>AVERAGE(V3:V15)</f>
-        <v>0.23076923076923078</v>
+        <v>47.846153846153847</v>
       </c>
       <c r="W16" s="5"/>
       <c r="X16" s="5"/>
@@ -1935,24 +1935,24 @@
         <v>1.1613545816733069</v>
       </c>
       <c r="F17" s="2">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="G17" s="2">
         <v>634</v>
       </c>
       <c r="H17" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.2629482071713147</v>
       </c>
       <c r="I17" s="2">
         <v>0</v>
       </c>
       <c r="J17" s="2">
-        <v>666</v>
+        <v>648</v>
       </c>
       <c r="K17" s="3">
         <f t="shared" si="4"/>
-        <v>1.3266932270916334</v>
+        <v>1.2908366533864541</v>
       </c>
       <c r="N17" s="5"/>
       <c r="O17" s="2" t="s">
@@ -1972,7 +1972,7 @@
       <c r="U17" s="5"/>
       <c r="V17" s="6">
         <f>AVERAGE(X4:X16)</f>
-        <v>1.2602485327766073</v>
+        <v>1.283779646487373</v>
       </c>
       <c r="W17" s="5"/>
       <c r="X17" s="5"/>
@@ -1995,17 +1995,17 @@
         <v>1.1605112301475424</v>
       </c>
       <c r="F18" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="G18" s="2">
         <v>26442</v>
       </c>
       <c r="H18" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.2424584155624472</v>
       </c>
       <c r="I18" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" s="2">
         <v>27210</v>
@@ -2033,17 +2033,17 @@
         <v>1.1402959178755603</v>
       </c>
       <c r="F19" s="2">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="G19" s="2">
         <v>27130</v>
       </c>
       <c r="H19" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.3075328931514771</v>
       </c>
       <c r="I19" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J19" s="2">
         <v>27968</v>
@@ -2071,17 +2071,17 @@
         <v>1.1670893209354747</v>
       </c>
       <c r="F20" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G20" s="2">
         <v>26002</v>
       </c>
       <c r="H20" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.2210951441720672</v>
       </c>
       <c r="I20" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" s="2">
         <v>27112</v>
@@ -2109,24 +2109,24 @@
         <v>1.2152159896840748</v>
       </c>
       <c r="F21" s="2">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G21" s="2">
         <v>10646</v>
       </c>
       <c r="H21" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.3727917472598323</v>
       </c>
       <c r="I21" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" s="2">
-        <v>10796</v>
+        <v>10798</v>
       </c>
       <c r="K21" s="3">
         <f t="shared" si="4"/>
-        <v>1.392134107027724</v>
+        <v>1.3923920051579626</v>
       </c>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.3">
@@ -2147,24 +2147,24 @@
         <v>1.1860095389507155</v>
       </c>
       <c r="F22" s="2">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="G22" s="2">
         <v>822</v>
       </c>
       <c r="H22" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.3068362480127187</v>
       </c>
       <c r="I22" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" s="2">
-        <v>855</v>
+        <v>835</v>
       </c>
       <c r="K22" s="3">
         <f t="shared" si="4"/>
-        <v>1.3593004769475359</v>
+        <v>1.3275039745627981</v>
       </c>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.3">
@@ -2185,24 +2185,24 @@
         <v>1.177759232213645</v>
       </c>
       <c r="F23" s="2">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="G23" s="2">
         <v>18901</v>
       </c>
       <c r="H23" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.3144864037832951</v>
       </c>
       <c r="I23" s="2">
         <v>0</v>
       </c>
       <c r="J23" s="2">
-        <v>19623</v>
+        <v>19495</v>
       </c>
       <c r="K23" s="3">
         <f t="shared" si="4"/>
-        <v>1.3646985186730649</v>
+        <v>1.3557966478892829</v>
       </c>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.3">
@@ -2223,24 +2223,24 @@
         <v>1.101379724055189</v>
       </c>
       <c r="F24" s="2">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="G24" s="2">
         <v>2101</v>
       </c>
       <c r="H24" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.2603479304139171</v>
       </c>
       <c r="I24" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" s="2">
-        <v>2149</v>
+        <v>2160</v>
       </c>
       <c r="K24" s="3">
         <f t="shared" si="4"/>
-        <v>1.2891421715656868</v>
+        <v>1.2957408518296341</v>
       </c>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.3">
@@ -2261,17 +2261,17 @@
         <v>1.1546273546273547</v>
       </c>
       <c r="F25" s="2">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="G25" s="2">
         <v>7906</v>
       </c>
       <c r="H25" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.2950040950040951</v>
       </c>
       <c r="I25" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J25" s="2">
         <v>8124</v>
@@ -2299,24 +2299,24 @@
         <v>1.105101884479853</v>
       </c>
       <c r="F26" s="2">
-        <v>416</v>
+        <v>437</v>
       </c>
       <c r="G26" s="2">
         <v>8140</v>
       </c>
       <c r="H26" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.24712731729738</v>
       </c>
       <c r="I26" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J26" s="2">
-        <v>8215</v>
+        <v>8148</v>
       </c>
       <c r="K26" s="3">
         <f t="shared" si="4"/>
-        <v>1.2586180481078597</v>
+        <v>1.2483529952504979</v>
       </c>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.3">
@@ -2337,24 +2337,24 @@
         <v>1.026266416510319</v>
       </c>
       <c r="F27" s="2">
-        <v>1306</v>
+        <v>1413</v>
       </c>
       <c r="G27" s="2">
         <v>588</v>
       </c>
       <c r="H27" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.1031894934333959</v>
       </c>
       <c r="I27" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J27" s="2">
-        <v>575</v>
+        <v>598</v>
       </c>
       <c r="K27" s="3">
         <f t="shared" si="4"/>
-        <v>1.0787992495309568</v>
+        <v>1.1219512195121952</v>
       </c>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.3">
@@ -2375,24 +2375,24 @@
         <v>1.2057602490918526</v>
       </c>
       <c r="F28" s="2">
-        <v>1989</v>
+        <v>2241</v>
       </c>
       <c r="G28" s="2">
         <v>5122</v>
       </c>
       <c r="H28" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.3290088220031135</v>
       </c>
       <c r="I28" s="2">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J28" s="2">
-        <v>5481</v>
+        <v>5243</v>
       </c>
       <c r="K28" s="3">
         <f t="shared" si="4"/>
-        <v>1.4221587960560456</v>
+        <v>1.3604047742605085</v>
       </c>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.3">
@@ -2413,24 +2413,24 @@
         <v>1.1535478867778208</v>
       </c>
       <c r="F29" s="2">
-        <v>4514</v>
+        <v>4774</v>
       </c>
       <c r="G29" s="2">
         <v>3313</v>
       </c>
       <c r="H29" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.2846064366033347</v>
       </c>
       <c r="I29" s="2">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J29" s="2">
-        <v>3565</v>
+        <v>3580</v>
       </c>
       <c r="K29" s="3">
         <f t="shared" si="4"/>
-        <v>1.3823187281892206</v>
+        <v>1.3881349360217139</v>
       </c>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.3">
@@ -2451,24 +2451,24 @@
         <v>1.1609358383551931</v>
       </c>
       <c r="F30" s="2">
-        <v>29490</v>
+        <v>39353</v>
       </c>
       <c r="G30" s="2">
         <v>68397</v>
       </c>
       <c r="H30" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.3469809760132341</v>
       </c>
       <c r="I30" s="2">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="J30" s="2">
-        <v>69347</v>
+        <v>69223</v>
       </c>
       <c r="K30" s="3">
         <f t="shared" si="4"/>
-        <v>1.3656898656898657</v>
+        <v>1.3632478632478633</v>
       </c>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.3">
@@ -2489,24 +2489,24 @@
         <v>1.2111602231272558</v>
       </c>
       <c r="F31" s="2">
-        <v>502354</v>
+        <v>696928</v>
       </c>
       <c r="G31" s="2">
         <v>347246</v>
       </c>
       <c r="H31" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.3404852438765464</v>
       </c>
       <c r="I31" s="2">
-        <v>3</v>
+        <v>519</v>
       </c>
       <c r="J31" s="2">
-        <v>345675</v>
+        <v>348709</v>
       </c>
       <c r="K31" s="3">
         <f t="shared" si="4"/>
-        <v>1.3344206605030013</v>
+        <v>1.3461329112702427</v>
       </c>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.3">
@@ -2524,13 +2524,13 @@
       <c r="E32" s="5"/>
       <c r="F32" s="6">
         <f>AVERAGE(F3:F31)</f>
-        <v>18661.03448275862</v>
+        <v>25735.551724137931</v>
       </c>
       <c r="G32" s="5"/>
       <c r="H32" s="5"/>
       <c r="I32" s="6">
         <f>AVERAGE(I3:I31)</f>
-        <v>0.10344827586206896</v>
+        <v>22.275862068965516</v>
       </c>
       <c r="J32" s="5"/>
       <c r="K32" s="5"/>
@@ -2554,7 +2554,7 @@
       <c r="H33" s="5"/>
       <c r="I33" s="6">
         <f>AVERAGE(K4:K32)</f>
-        <v>1.283560426015834</v>
+        <v>1.2892511431702736</v>
       </c>
       <c r="J33" s="5"/>
       <c r="K33" s="5"/>
@@ -2564,6 +2564,23 @@
     <sortCondition ref="F3:F31"/>
   </sortState>
   <mergeCells count="24">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="I32:K32"/>
+    <mergeCell ref="I33:K33"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:R1"/>
+    <mergeCell ref="S1:U1"/>
+    <mergeCell ref="V1:X1"/>
     <mergeCell ref="N16:N17"/>
     <mergeCell ref="P16:R16"/>
     <mergeCell ref="S16:U16"/>
@@ -2571,23 +2588,6 @@
     <mergeCell ref="P17:R17"/>
     <mergeCell ref="S17:U17"/>
     <mergeCell ref="V17:X17"/>
-    <mergeCell ref="N1:N2"/>
-    <mergeCell ref="O1:O2"/>
-    <mergeCell ref="P1:R1"/>
-    <mergeCell ref="S1:U1"/>
-    <mergeCell ref="V1:X1"/>
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="I32:K32"/>
-    <mergeCell ref="I33:K33"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="C32:E32"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="C33:E33"/>
-    <mergeCell ref="F33:H33"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/resource/result.xlsx
+++ b/resource/result.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_Files\_Lessons\ALGORITHM\Project\resource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DD0BCDD-4C87-4B82-B61B-58E0B8F848A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C20CFAFF-D0D8-4194-8206-2761D7ED209A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXACT" sheetId="9" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="51">
   <si>
     <t>att48</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -228,6 +228,12 @@
   <si>
     <t>MST-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>min_cost</t>
+  </si>
+  <si>
+    <t>ratio</t>
   </si>
 </sst>
 </file>
@@ -288,7 +294,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -308,6 +314,12 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -323,6 +335,1574 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="zh-CN"/>
+              <a:t>近似比随数据规模变化图</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="9.1206036745406824E-2"/>
+          <c:y val="0.18039370078740158"/>
+          <c:w val="0.88475306211723537"/>
+          <c:h val="0.60613954505686785"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>APPRO!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>greedy</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>APPRO!$A$3:$A$31</c:f>
+              <c:strCache>
+                <c:ptCount val="29"/>
+                <c:pt idx="0">
+                  <c:v>five5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>p15</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>ulysses16</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>gr17</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>ulysses22</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>fri26</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>bayg29</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>bays29</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>att48</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>eil51</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>berlin52</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>st70</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>eil76</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>pr76</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>gr96</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>kroA100</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>kroC100</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>kroD100</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>rd100</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>eil101</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>lin105</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>gr120</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>ch130</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>ch150</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>gr202</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>tsp225</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>a280</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>pcb442</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>pr1002</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>APPRO!$E$3:$E$31</c:f>
+              <c:numCache>
+                <c:formatCode>0.00_ </c:formatCode>
+                <c:ptCount val="29"/>
+                <c:pt idx="0">
+                  <c:v>1.1052631578947369</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.0422535211267605</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.0446043165467627</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.178082191780822</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.0298826040554963</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.0979830265623278</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.0723358449946179</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.1314023207946782</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.1314553990610328</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.0847255369928401</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.1792592592592592</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.1301115241635689</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.2104494309303895</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.1613545816733069</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.1605112301475424</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1.1402959178755603</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1.1670893209354747</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1.2152159896840748</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1.1860095389507155</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1.177759232213645</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1.101379724055189</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1.1546273546273547</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1.105101884479853</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1.026266416510319</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1.2057602490918526</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1.1535478867778208</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1.1609358383551931</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1.2111602231272558</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2AF0-44D4-B3C0-27BAF885836E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>APPRO!$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>MST-0</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>APPRO!$A$3:$A$31</c:f>
+              <c:strCache>
+                <c:ptCount val="29"/>
+                <c:pt idx="0">
+                  <c:v>five5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>p15</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>ulysses16</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>gr17</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>ulysses22</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>fri26</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>bayg29</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>bays29</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>att48</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>eil51</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>berlin52</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>st70</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>eil76</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>pr76</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>gr96</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>kroA100</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>kroC100</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>kroD100</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>rd100</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>eil101</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>lin105</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>gr120</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>ch130</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>ch150</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>gr202</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>tsp225</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>a280</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>pcb442</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>pr1002</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>APPRO!$H$3:$H$31</c:f>
+              <c:numCache>
+                <c:formatCode>0.00_ </c:formatCode>
+                <c:ptCount val="29"/>
+                <c:pt idx="0">
+                  <c:v>1.1052631578947369</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.0274914089347078</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.0140845070422535</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.0599520383693046</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.0273972602739727</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.176093916755603</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.1397553179764135</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.1131324004305705</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.2287086477940519</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.3051643192488263</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.2662423760275789</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.277037037037037</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.2527881040892193</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.3136678408639133</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.2629482071713147</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.2424584155624472</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1.3075328931514771</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1.2210951441720672</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1.3727917472598323</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1.3068362480127187</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1.3144864037832951</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1.2603479304139171</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1.2950040950040951</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1.24712731729738</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1.1031894934333959</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1.3290088220031135</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1.2846064366033347</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1.3469809760132341</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1.3404852438765464</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-2AF0-44D4-B3C0-27BAF885836E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>APPRO!$I$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>MST-1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>APPRO!$A$3:$A$31</c:f>
+              <c:strCache>
+                <c:ptCount val="29"/>
+                <c:pt idx="0">
+                  <c:v>five5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>p15</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>ulysses16</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>gr17</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>ulysses22</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>fri26</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>bayg29</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>bays29</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>att48</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>eil51</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>berlin52</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>st70</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>eil76</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>pr76</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>gr96</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>kroA100</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>kroC100</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>kroD100</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>rd100</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>eil101</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>lin105</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>gr120</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>ch130</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>ch150</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>gr202</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>tsp225</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>a280</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>pcb442</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>pr1002</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>APPRO!$K$3:$K$31</c:f>
+              <c:numCache>
+                <c:formatCode>0.00_ </c:formatCode>
+                <c:ptCount val="29"/>
+                <c:pt idx="0">
+                  <c:v>1.2105263157894737</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.2577319587628866</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.1126760563380282</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.1280575539568345</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.1369863013698631</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.1867662753468518</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.3018847128843822</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.2714747039827772</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.31175610774692</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.3708920187793427</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.3410236011667993</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.3214814814814815</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.2936802973977695</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.3437254412485322</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.2908366533864541</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.2785452495066254</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1.3479203817051424</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1.2732225039917349</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1.3923920051579626</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1.3275039745627981</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1.3557966478892829</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1.2957408518296341</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1.3307125307125307</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1.2483529952504979</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1.1219512195121952</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1.3604047742605085</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1.3881349360217139</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1.3632478632478633</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1.3461329112702427</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-2AF0-44D4-B3C0-27BAF885836E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="2135659376"/>
+        <c:axId val="2135657456"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="2135659376"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-3000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2135657456"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="2135657456"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1.4"/>
+          <c:min val="1"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00_ " sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2135659376"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.27900000000000003"/>
+          <c:y val="0.12347149314669"/>
+          <c:w val="0.44600000000000001"/>
+          <c:h val="7.6969233012540106E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-CN"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>311150</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>260350</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="图表 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8AAD7746-EAC6-5CDE-CFA5-97FBE866E78B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -814,24 +2394,24 @@
       <c r="N1" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="O1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="P1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="Q1" s="5"/>
-      <c r="R1" s="5"/>
-      <c r="S1" s="5" t="s">
+      <c r="Q1" s="7"/>
+      <c r="R1" s="7"/>
+      <c r="S1" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="T1" s="5"/>
-      <c r="U1" s="5"/>
-      <c r="V1" s="5" t="s">
+      <c r="T1" s="7"/>
+      <c r="U1" s="7"/>
+      <c r="V1" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="W1" s="5"/>
-      <c r="X1" s="5"/>
+      <c r="W1" s="7"/>
+      <c r="X1" s="7"/>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A2" s="5"/>
@@ -864,33 +2444,33 @@
         <v>9</v>
       </c>
       <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="2" t="s">
+      <c r="O2" s="7"/>
+      <c r="P2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="Q2" s="2" t="s">
-        <v>8</v>
+      <c r="Q2" s="8" t="s">
+        <v>49</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="S2" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="T2" s="2" t="s">
-        <v>8</v>
+      <c r="T2" s="8" t="s">
+        <v>49</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="V2" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="V2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="W2" s="2" t="s">
-        <v>8</v>
+      <c r="W2" s="8" t="s">
+        <v>49</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>9</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.3">
@@ -933,37 +2513,34 @@
       <c r="N3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="O3" s="2">
+      <c r="O3" s="8">
         <v>19</v>
       </c>
-      <c r="P3" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="2">
+      <c r="P3" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="8">
         <v>21</v>
       </c>
       <c r="R3" s="3">
-        <f t="shared" ref="R3:R4" si="1">Q3/O3</f>
         <v>1.1052631578947369</v>
       </c>
-      <c r="S3" s="2">
-        <v>0</v>
-      </c>
-      <c r="T3" s="2">
+      <c r="S3" s="8">
+        <v>0</v>
+      </c>
+      <c r="T3" s="8">
         <v>21</v>
       </c>
       <c r="U3" s="3">
-        <f t="shared" ref="U3:U4" si="2">T3/O3</f>
         <v>1.1052631578947369</v>
       </c>
-      <c r="V3" s="2">
-        <v>0</v>
-      </c>
-      <c r="W3" s="2">
+      <c r="V3" s="8">
+        <v>0</v>
+      </c>
+      <c r="W3" s="8">
         <v>23</v>
       </c>
       <c r="X3" s="3">
-        <f>W3/O3</f>
         <v>1.2105263157894737</v>
       </c>
     </row>
@@ -991,7 +2568,7 @@
         <v>299</v>
       </c>
       <c r="H4" s="3">
-        <f t="shared" ref="H4:H31" si="3">G4/B4</f>
+        <f t="shared" ref="H4:H31" si="1">G4/B4</f>
         <v>1.0274914089347078</v>
       </c>
       <c r="I4" s="2">
@@ -1001,43 +2578,40 @@
         <v>366</v>
       </c>
       <c r="K4" s="3">
-        <f t="shared" ref="K4:K31" si="4">J4/B4</f>
+        <f t="shared" ref="K4:K31" si="2">J4/B4</f>
         <v>1.2577319587628866</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="O4" s="2">
+      <c r="O4" s="8">
         <v>291</v>
       </c>
-      <c r="P4" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="2">
+      <c r="P4" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="8">
         <v>291</v>
       </c>
       <c r="R4" s="3">
-        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="S4" s="2">
-        <v>0</v>
-      </c>
-      <c r="T4" s="2">
+      <c r="S4" s="8">
+        <v>0</v>
+      </c>
+      <c r="T4" s="8">
         <v>299</v>
       </c>
       <c r="U4" s="3">
-        <f t="shared" si="2"/>
         <v>1.0274914089347078</v>
       </c>
-      <c r="V4" s="2">
-        <v>0</v>
-      </c>
-      <c r="W4" s="2">
+      <c r="V4" s="8">
+        <v>0</v>
+      </c>
+      <c r="W4" s="8">
         <v>366</v>
       </c>
       <c r="X4" s="3">
-        <f t="shared" ref="X4" si="5">W4/O4</f>
         <v>1.2577319587628866</v>
       </c>
     </row>
@@ -1065,7 +2639,7 @@
         <v>72</v>
       </c>
       <c r="H5" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.0140845070422535</v>
       </c>
       <c r="I5" s="2">
@@ -1075,43 +2649,40 @@
         <v>79</v>
       </c>
       <c r="K5" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1.1126760563380282</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="O5" s="2">
+      <c r="O5" s="8">
         <v>937</v>
       </c>
-      <c r="P5" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="2">
+      <c r="P5" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="8">
         <v>965</v>
       </c>
       <c r="R5" s="3">
-        <f t="shared" ref="R5:R15" si="6">Q5/O5</f>
         <v>1.0298826040554963</v>
       </c>
-      <c r="S5" s="2">
+      <c r="S5" s="8">
         <v>1</v>
       </c>
-      <c r="T5" s="2">
+      <c r="T5" s="8">
         <v>1102</v>
       </c>
       <c r="U5" s="3">
-        <f t="shared" ref="U5:U15" si="7">T5/O5</f>
         <v>1.176093916755603</v>
       </c>
-      <c r="V5" s="2">
-        <v>0</v>
-      </c>
-      <c r="W5" s="2">
+      <c r="V5" s="8">
+        <v>0</v>
+      </c>
+      <c r="W5" s="8">
         <v>1112</v>
       </c>
       <c r="X5" s="3">
-        <f t="shared" ref="X5:X15" si="8">W5/O5</f>
         <v>1.1867662753468518</v>
       </c>
     </row>
@@ -1139,7 +2710,7 @@
         <v>2210</v>
       </c>
       <c r="H6" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.0599520383693046</v>
       </c>
       <c r="I6" s="2">
@@ -1149,43 +2720,40 @@
         <v>2352</v>
       </c>
       <c r="K6" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1.1280575539568345</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="O6" s="2">
+      <c r="O6" s="8">
         <v>33523</v>
       </c>
-      <c r="P6" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="2">
+      <c r="P6" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="8">
         <v>37928</v>
       </c>
       <c r="R6" s="3">
-        <f t="shared" si="6"/>
         <v>1.1314023207946782</v>
       </c>
-      <c r="S6" s="2">
+      <c r="S6" s="8">
         <v>5</v>
       </c>
-      <c r="T6" s="2">
+      <c r="T6" s="8">
         <v>41190</v>
       </c>
       <c r="U6" s="3">
-        <f t="shared" si="7"/>
         <v>1.2287086477940519</v>
       </c>
-      <c r="V6" s="2">
-        <v>0</v>
-      </c>
-      <c r="W6" s="2">
+      <c r="V6" s="8">
+        <v>0</v>
+      </c>
+      <c r="W6" s="8">
         <v>43974</v>
       </c>
       <c r="X6" s="3">
-        <f t="shared" si="8"/>
         <v>1.31175610774692</v>
       </c>
     </row>
@@ -1213,7 +2781,7 @@
         <v>75</v>
       </c>
       <c r="H7" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.0273972602739727</v>
       </c>
       <c r="I7" s="2">
@@ -1223,43 +2791,40 @@
         <v>83</v>
       </c>
       <c r="K7" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1.1369863013698631</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="O7" s="2">
+      <c r="O7" s="8">
         <v>675</v>
       </c>
-      <c r="P7" s="2">
+      <c r="P7" s="8">
         <v>1</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="Q7" s="8">
         <v>796</v>
       </c>
       <c r="R7" s="3">
-        <f t="shared" si="6"/>
         <v>1.1792592592592592</v>
       </c>
-      <c r="S7" s="2">
+      <c r="S7" s="8">
         <v>27</v>
       </c>
-      <c r="T7" s="2">
+      <c r="T7" s="8">
         <v>862</v>
       </c>
       <c r="U7" s="3">
-        <f t="shared" si="7"/>
         <v>1.277037037037037</v>
       </c>
-      <c r="V7" s="2">
-        <v>0</v>
-      </c>
-      <c r="W7" s="2">
+      <c r="V7" s="8">
+        <v>0</v>
+      </c>
+      <c r="W7" s="8">
         <v>892</v>
       </c>
       <c r="X7" s="3">
-        <f t="shared" si="8"/>
         <v>1.3214814814814815</v>
       </c>
     </row>
@@ -1287,7 +2852,7 @@
         <v>1102</v>
       </c>
       <c r="H8" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.176093916755603</v>
       </c>
       <c r="I8" s="2">
@@ -1297,43 +2862,40 @@
         <v>1112</v>
       </c>
       <c r="K8" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1.1867662753468518</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="O8" s="2">
+      <c r="O8" s="8">
         <v>502</v>
       </c>
-      <c r="P8" s="2">
+      <c r="P8" s="8">
         <v>2</v>
       </c>
-      <c r="Q8" s="2">
+      <c r="Q8" s="8">
         <v>583</v>
       </c>
       <c r="R8" s="3">
-        <f t="shared" si="6"/>
         <v>1.1613545816733069</v>
       </c>
-      <c r="S8" s="2">
+      <c r="S8" s="8">
         <v>76</v>
       </c>
-      <c r="T8" s="2">
+      <c r="T8" s="8">
         <v>634</v>
       </c>
       <c r="U8" s="3">
-        <f t="shared" si="7"/>
         <v>1.2629482071713147</v>
       </c>
-      <c r="V8" s="2">
-        <v>0</v>
-      </c>
-      <c r="W8" s="2">
+      <c r="V8" s="8">
+        <v>0</v>
+      </c>
+      <c r="W8" s="8">
         <v>648</v>
       </c>
       <c r="X8" s="3">
-        <f t="shared" si="8"/>
         <v>1.2908366533864541</v>
       </c>
     </row>
@@ -1361,7 +2923,7 @@
         <v>10341</v>
       </c>
       <c r="H9" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.1397553179764135</v>
       </c>
       <c r="I9" s="2">
@@ -1371,7 +2933,7 @@
         <v>11812</v>
       </c>
       <c r="K9" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1.3018847128843822</v>
       </c>
       <c r="N9" s="2" t="s">
@@ -1387,7 +2949,7 @@
         <v>24852</v>
       </c>
       <c r="R9" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="R5:R15" si="3">Q9/O9</f>
         <v>1.1670893209354747</v>
       </c>
       <c r="S9" s="2">
@@ -1397,7 +2959,7 @@
         <v>26002</v>
       </c>
       <c r="U9" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="U5:U15" si="4">T9/O9</f>
         <v>1.2210951441720672</v>
       </c>
       <c r="V9" s="2">
@@ -1407,7 +2969,7 @@
         <v>27112</v>
       </c>
       <c r="X9" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="X5:X15" si="5">W9/O9</f>
         <v>1.2732225039917349</v>
       </c>
     </row>
@@ -1435,7 +2997,7 @@
         <v>10341</v>
       </c>
       <c r="H10" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.1131324004305705</v>
       </c>
       <c r="I10" s="2">
@@ -1445,7 +3007,7 @@
         <v>11812</v>
       </c>
       <c r="K10" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1.2714747039827772</v>
       </c>
       <c r="N10" s="2" t="s">
@@ -1461,7 +3023,7 @@
         <v>1836</v>
       </c>
       <c r="R10" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>1.101379724055189</v>
       </c>
       <c r="S10" s="2">
@@ -1471,7 +3033,7 @@
         <v>2101</v>
       </c>
       <c r="U10" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>1.2603479304139171</v>
       </c>
       <c r="V10" s="2">
@@ -1481,7 +3043,7 @@
         <v>2160</v>
       </c>
       <c r="X10" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>1.2957408518296341</v>
       </c>
     </row>
@@ -1509,7 +3071,7 @@
         <v>41190</v>
       </c>
       <c r="H11" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.2287086477940519</v>
       </c>
       <c r="I11" s="2">
@@ -1519,7 +3081,7 @@
         <v>43974</v>
       </c>
       <c r="K11" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1.31175610774692</v>
       </c>
       <c r="N11" s="2" t="s">
@@ -1535,7 +3097,7 @@
         <v>7213</v>
       </c>
       <c r="R11" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>1.105101884479853</v>
       </c>
       <c r="S11" s="2">
@@ -1545,7 +3107,7 @@
         <v>8140</v>
       </c>
       <c r="U11" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>1.24712731729738</v>
       </c>
       <c r="V11" s="2">
@@ -1555,7 +3117,7 @@
         <v>8148</v>
       </c>
       <c r="X11" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>1.2483529952504979</v>
       </c>
     </row>
@@ -1583,7 +3145,7 @@
         <v>556</v>
       </c>
       <c r="H12" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.3051643192488263</v>
       </c>
       <c r="I12" s="2">
@@ -1593,7 +3155,7 @@
         <v>584</v>
       </c>
       <c r="K12" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1.3708920187793427</v>
       </c>
       <c r="N12" s="2" t="s">
@@ -1609,7 +3171,7 @@
         <v>547</v>
       </c>
       <c r="R12" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>1.026266416510319</v>
       </c>
       <c r="S12" s="2">
@@ -1619,7 +3181,7 @@
         <v>588</v>
       </c>
       <c r="U12" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>1.1031894934333959</v>
       </c>
       <c r="V12" s="2">
@@ -1629,7 +3191,7 @@
         <v>598</v>
       </c>
       <c r="X12" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>1.1219512195121952</v>
       </c>
     </row>
@@ -1657,7 +3219,7 @@
         <v>9550</v>
       </c>
       <c r="H13" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.2662423760275789</v>
       </c>
       <c r="I13" s="2">
@@ -1667,7 +3229,7 @@
         <v>10114</v>
       </c>
       <c r="K13" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1.3410236011667993</v>
       </c>
       <c r="N13" s="2" t="s">
@@ -1683,7 +3245,7 @@
         <v>2975</v>
       </c>
       <c r="R13" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>1.1535478867778208</v>
       </c>
       <c r="S13" s="2">
@@ -1693,7 +3255,7 @@
         <v>3313</v>
       </c>
       <c r="U13" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>1.2846064366033347</v>
       </c>
       <c r="V13" s="2">
@@ -1703,7 +3265,7 @@
         <v>3580</v>
       </c>
       <c r="X13" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>1.3881349360217139</v>
       </c>
     </row>
@@ -1731,7 +3293,7 @@
         <v>862</v>
       </c>
       <c r="H14" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.277037037037037</v>
       </c>
       <c r="I14" s="2">
@@ -1741,7 +3303,7 @@
         <v>892</v>
       </c>
       <c r="K14" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1.3214814814814815</v>
       </c>
       <c r="N14" s="2" t="s">
@@ -1757,7 +3319,7 @@
         <v>58950</v>
       </c>
       <c r="R14" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>1.1609358383551931</v>
       </c>
       <c r="S14" s="2">
@@ -1767,7 +3329,7 @@
         <v>68397</v>
       </c>
       <c r="U14" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>1.3469809760132341</v>
       </c>
       <c r="V14" s="2">
@@ -1777,7 +3339,7 @@
         <v>69223</v>
       </c>
       <c r="X14" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>1.3632478632478633</v>
       </c>
     </row>
@@ -1805,7 +3367,7 @@
         <v>674</v>
       </c>
       <c r="H15" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.2527881040892193</v>
       </c>
       <c r="I15" s="2">
@@ -1815,7 +3377,7 @@
         <v>696</v>
       </c>
       <c r="K15" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1.2936802973977695</v>
       </c>
       <c r="N15" s="2" t="s">
@@ -1831,7 +3393,7 @@
         <v>313745</v>
       </c>
       <c r="R15" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>1.2111602231272558</v>
       </c>
       <c r="S15" s="2">
@@ -1841,7 +3403,7 @@
         <v>347246</v>
       </c>
       <c r="U15" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>1.3404852438765464</v>
       </c>
       <c r="V15" s="2">
@@ -1851,7 +3413,7 @@
         <v>348709</v>
       </c>
       <c r="X15" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>1.3461329112702427</v>
       </c>
     </row>
@@ -1879,7 +3441,7 @@
         <v>142085</v>
       </c>
       <c r="H16" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.3136678408639133</v>
       </c>
       <c r="I16" s="2">
@@ -1889,7 +3451,7 @@
         <v>145336</v>
       </c>
       <c r="K16" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1.3437254412485322</v>
       </c>
       <c r="N16" s="5" t="s">
@@ -1941,7 +3503,7 @@
         <v>634</v>
       </c>
       <c r="H17" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.2629482071713147</v>
       </c>
       <c r="I17" s="2">
@@ -1951,7 +3513,7 @@
         <v>648</v>
       </c>
       <c r="K17" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1.2908366533864541</v>
       </c>
       <c r="N17" s="5"/>
@@ -2001,7 +3563,7 @@
         <v>26442</v>
       </c>
       <c r="H18" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.2424584155624472</v>
       </c>
       <c r="I18" s="2">
@@ -2011,7 +3573,7 @@
         <v>27210</v>
       </c>
       <c r="K18" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1.2785452495066254</v>
       </c>
     </row>
@@ -2039,7 +3601,7 @@
         <v>27130</v>
       </c>
       <c r="H19" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.3075328931514771</v>
       </c>
       <c r="I19" s="2">
@@ -2049,7 +3611,7 @@
         <v>27968</v>
       </c>
       <c r="K19" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1.3479203817051424</v>
       </c>
     </row>
@@ -2077,7 +3639,7 @@
         <v>26002</v>
       </c>
       <c r="H20" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.2210951441720672</v>
       </c>
       <c r="I20" s="2">
@@ -2087,7 +3649,7 @@
         <v>27112</v>
       </c>
       <c r="K20" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1.2732225039917349</v>
       </c>
     </row>
@@ -2115,7 +3677,7 @@
         <v>10646</v>
       </c>
       <c r="H21" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.3727917472598323</v>
       </c>
       <c r="I21" s="2">
@@ -2125,7 +3687,7 @@
         <v>10798</v>
       </c>
       <c r="K21" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1.3923920051579626</v>
       </c>
     </row>
@@ -2153,7 +3715,7 @@
         <v>822</v>
       </c>
       <c r="H22" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.3068362480127187</v>
       </c>
       <c r="I22" s="2">
@@ -2163,7 +3725,7 @@
         <v>835</v>
       </c>
       <c r="K22" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1.3275039745627981</v>
       </c>
     </row>
@@ -2191,7 +3753,7 @@
         <v>18901</v>
       </c>
       <c r="H23" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.3144864037832951</v>
       </c>
       <c r="I23" s="2">
@@ -2201,7 +3763,7 @@
         <v>19495</v>
       </c>
       <c r="K23" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1.3557966478892829</v>
       </c>
     </row>
@@ -2229,7 +3791,7 @@
         <v>2101</v>
       </c>
       <c r="H24" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.2603479304139171</v>
       </c>
       <c r="I24" s="2">
@@ -2239,7 +3801,7 @@
         <v>2160</v>
       </c>
       <c r="K24" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1.2957408518296341</v>
       </c>
     </row>
@@ -2267,7 +3829,7 @@
         <v>7906</v>
       </c>
       <c r="H25" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.2950040950040951</v>
       </c>
       <c r="I25" s="2">
@@ -2277,7 +3839,7 @@
         <v>8124</v>
       </c>
       <c r="K25" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1.3307125307125307</v>
       </c>
     </row>
@@ -2305,7 +3867,7 @@
         <v>8140</v>
       </c>
       <c r="H26" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.24712731729738</v>
       </c>
       <c r="I26" s="2">
@@ -2315,7 +3877,7 @@
         <v>8148</v>
       </c>
       <c r="K26" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1.2483529952504979</v>
       </c>
     </row>
@@ -2343,7 +3905,7 @@
         <v>588</v>
       </c>
       <c r="H27" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.1031894934333959</v>
       </c>
       <c r="I27" s="2">
@@ -2353,7 +3915,7 @@
         <v>598</v>
       </c>
       <c r="K27" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1.1219512195121952</v>
       </c>
     </row>
@@ -2381,7 +3943,7 @@
         <v>5122</v>
       </c>
       <c r="H28" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.3290088220031135</v>
       </c>
       <c r="I28" s="2">
@@ -2391,7 +3953,7 @@
         <v>5243</v>
       </c>
       <c r="K28" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1.3604047742605085</v>
       </c>
     </row>
@@ -2419,7 +3981,7 @@
         <v>3313</v>
       </c>
       <c r="H29" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.2846064366033347</v>
       </c>
       <c r="I29" s="2">
@@ -2429,7 +3991,7 @@
         <v>3580</v>
       </c>
       <c r="K29" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1.3881349360217139</v>
       </c>
     </row>
@@ -2457,7 +4019,7 @@
         <v>68397</v>
       </c>
       <c r="H30" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.3469809760132341</v>
       </c>
       <c r="I30" s="2">
@@ -2467,7 +4029,7 @@
         <v>69223</v>
       </c>
       <c r="K30" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1.3632478632478633</v>
       </c>
     </row>
@@ -2495,7 +4057,7 @@
         <v>347246</v>
       </c>
       <c r="H31" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.3404852438765464</v>
       </c>
       <c r="I31" s="2">
@@ -2505,7 +4067,7 @@
         <v>348709</v>
       </c>
       <c r="K31" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1.3461329112702427</v>
       </c>
     </row>
@@ -2591,5 +4153,7 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>